--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119625133</v>
+        <v>119624681</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451511</v>
+        <v>451658</v>
       </c>
       <c r="R2" t="n">
-        <v>6795545</v>
+        <v>6795526</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119624681</v>
+        <v>119625133</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451658</v>
+        <v>451511</v>
       </c>
       <c r="R3" t="n">
-        <v>6795526</v>
+        <v>6795545</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119624681</v>
+        <v>119623199</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90106</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>5754</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451658</v>
+        <v>452026</v>
       </c>
       <c r="R2" t="n">
-        <v>6795526</v>
+        <v>6795405</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119625133</v>
+        <v>119623275</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451511</v>
+        <v>452021</v>
       </c>
       <c r="R3" t="n">
-        <v>6795545</v>
+        <v>6795414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119623805</v>
+        <v>119623309</v>
       </c>
       <c r="B4" t="n">
-        <v>94311</v>
+        <v>91494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451965</v>
+        <v>451996</v>
       </c>
       <c r="R4" t="n">
-        <v>6795388</v>
+        <v>6795413</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119623199</v>
+        <v>119622912</v>
       </c>
       <c r="B5" t="n">
-        <v>90106</v>
+        <v>104994</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5754</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452026</v>
+        <v>452035</v>
       </c>
       <c r="R5" t="n">
-        <v>6795405</v>
+        <v>6795377</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119623971</v>
+        <v>119624025</v>
       </c>
       <c r="B6" t="n">
-        <v>104994</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451957</v>
+        <v>451942</v>
       </c>
       <c r="R6" t="n">
-        <v>6795424</v>
+        <v>6795447</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119623275</v>
+        <v>119625094</v>
       </c>
       <c r="B7" t="n">
-        <v>90334</v>
+        <v>90527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452021</v>
+        <v>451529</v>
       </c>
       <c r="R7" t="n">
-        <v>6795414</v>
+        <v>6795557</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119623113</v>
+        <v>119624681</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452038</v>
+        <v>451658</v>
       </c>
       <c r="R8" t="n">
-        <v>6795402</v>
+        <v>6795526</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119623701</v>
+        <v>119623301</v>
       </c>
       <c r="B9" t="n">
-        <v>91494</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452000</v>
+        <v>452006</v>
       </c>
       <c r="R9" t="n">
-        <v>6795356</v>
+        <v>6795400</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119624582</v>
+        <v>119623971</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>104994</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1503,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451684</v>
+        <v>451957</v>
       </c>
       <c r="R10" t="n">
-        <v>6795469</v>
+        <v>6795424</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119624105</v>
+        <v>119624582</v>
       </c>
       <c r="B11" t="n">
-        <v>94311</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451926</v>
+        <v>451684</v>
       </c>
       <c r="R11" t="n">
-        <v>6795450</v>
+        <v>6795469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1669,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kallkällor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119623301</v>
+        <v>119624986</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,38 +1707,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452006</v>
+        <v>451575</v>
       </c>
       <c r="R12" t="n">
-        <v>6795400</v>
+        <v>6795592</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119624141</v>
+        <v>119623113</v>
       </c>
       <c r="B13" t="n">
         <v>91494</v>
@@ -1842,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451909</v>
+        <v>452038</v>
       </c>
       <c r="R13" t="n">
-        <v>6795438</v>
+        <v>6795402</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1873,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Invid en kallkälla.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119623430</v>
+        <v>119624110</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,47 +1911,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452010</v>
+        <v>451915</v>
       </c>
       <c r="R14" t="n">
-        <v>6795395</v>
+        <v>6795444</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119623309</v>
+        <v>119625963</v>
       </c>
       <c r="B15" t="n">
-        <v>91494</v>
+        <v>82305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,38 +2013,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451996</v>
+        <v>451704</v>
       </c>
       <c r="R15" t="n">
-        <v>6795413</v>
+        <v>6795497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119624986</v>
+        <v>119623805</v>
       </c>
       <c r="B16" t="n">
-        <v>91254</v>
+        <v>94311</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,34 +2119,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451575</v>
+        <v>451965</v>
       </c>
       <c r="R16" t="n">
-        <v>6795592</v>
+        <v>6795388</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119625094</v>
+        <v>119623701</v>
       </c>
       <c r="B17" t="n">
-        <v>90527</v>
+        <v>91494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,34 +2221,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451529</v>
+        <v>452000</v>
       </c>
       <c r="R17" t="n">
-        <v>6795557</v>
+        <v>6795356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119624110</v>
+        <v>119624105</v>
       </c>
       <c r="B18" t="n">
-        <v>90334</v>
+        <v>94311</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2342,21 +2323,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3215</v>
+        <v>2809</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451915</v>
+        <v>451926</v>
       </c>
       <c r="R18" t="n">
-        <v>6795444</v>
+        <v>6795450</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,6 +2383,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Kallkällor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2428,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119625963</v>
+        <v>119625133</v>
       </c>
       <c r="B19" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451704</v>
+        <v>451511</v>
       </c>
       <c r="R19" t="n">
-        <v>6795497</v>
+        <v>6795545</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,10 +2516,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119624025</v>
+        <v>119623430</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,38 +2528,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451942</v>
+        <v>452010</v>
       </c>
       <c r="R20" t="n">
-        <v>6795447</v>
+        <v>6795395</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119622912</v>
+        <v>119624141</v>
       </c>
       <c r="B21" t="n">
-        <v>104994</v>
+        <v>91494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2648,21 +2643,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452035</v>
+        <v>451909</v>
       </c>
       <c r="R21" t="n">
-        <v>6795377</v>
+        <v>6795438</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2708,6 +2703,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Invid en kallkälla.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119624582</v>
+        <v>119624986</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>91254</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451684</v>
+        <v>451575</v>
       </c>
       <c r="R11" t="n">
-        <v>6795469</v>
+        <v>6795592</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119624986</v>
+        <v>119624582</v>
       </c>
       <c r="B12" t="n">
-        <v>91254</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451575</v>
+        <v>451684</v>
       </c>
       <c r="R12" t="n">
-        <v>6795592</v>
+        <v>6795469</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119623199</v>
+        <v>119623805</v>
       </c>
       <c r="B2" t="n">
-        <v>90106</v>
+        <v>94311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5754</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452026</v>
+        <v>451965</v>
       </c>
       <c r="R2" t="n">
-        <v>6795405</v>
+        <v>6795388</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119623309</v>
+        <v>119624110</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>90334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451996</v>
+        <v>451915</v>
       </c>
       <c r="R4" t="n">
-        <v>6795413</v>
+        <v>6795444</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119624025</v>
+        <v>119624582</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1119,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451942</v>
+        <v>451684</v>
       </c>
       <c r="R6" t="n">
-        <v>6795447</v>
+        <v>6795469</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119625094</v>
+        <v>119623309</v>
       </c>
       <c r="B7" t="n">
-        <v>90527</v>
+        <v>91494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451529</v>
+        <v>451996</v>
       </c>
       <c r="R7" t="n">
-        <v>6795557</v>
+        <v>6795413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119624681</v>
+        <v>119623113</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>91494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,38 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451658</v>
+        <v>452038</v>
       </c>
       <c r="R8" t="n">
-        <v>6795526</v>
+        <v>6795402</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119623301</v>
+        <v>119623199</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>90106</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5754</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452006</v>
+        <v>452026</v>
       </c>
       <c r="R9" t="n">
-        <v>6795400</v>
+        <v>6795405</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119623971</v>
+        <v>119623301</v>
       </c>
       <c r="B10" t="n">
-        <v>104994</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451957</v>
+        <v>452006</v>
       </c>
       <c r="R10" t="n">
-        <v>6795424</v>
+        <v>6795400</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119624986</v>
+        <v>119624105</v>
       </c>
       <c r="B11" t="n">
-        <v>91254</v>
+        <v>94311</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,34 +1609,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451575</v>
+        <v>451926</v>
       </c>
       <c r="R11" t="n">
-        <v>6795592</v>
+        <v>6795450</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kallkällor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119624582</v>
+        <v>119625963</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451684</v>
+        <v>451704</v>
       </c>
       <c r="R12" t="n">
-        <v>6795469</v>
+        <v>6795497</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119623113</v>
+        <v>119624986</v>
       </c>
       <c r="B13" t="n">
-        <v>91494</v>
+        <v>91254</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,34 +1818,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452038</v>
+        <v>451575</v>
       </c>
       <c r="R13" t="n">
-        <v>6795402</v>
+        <v>6795592</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119624110</v>
+        <v>119624681</v>
       </c>
       <c r="B14" t="n">
-        <v>90334</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,38 +1916,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3215</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451915</v>
+        <v>451658</v>
       </c>
       <c r="R14" t="n">
-        <v>6795444</v>
+        <v>6795526</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119625963</v>
+        <v>119624141</v>
       </c>
       <c r="B15" t="n">
-        <v>82305</v>
+        <v>91494</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,38 +2018,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451704</v>
+        <v>451909</v>
       </c>
       <c r="R15" t="n">
-        <v>6795497</v>
+        <v>6795438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,6 +2082,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Invid en kallkälla.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119623805</v>
+        <v>119623701</v>
       </c>
       <c r="B16" t="n">
-        <v>94311</v>
+        <v>91494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451965</v>
+        <v>452000</v>
       </c>
       <c r="R16" t="n">
-        <v>6795388</v>
+        <v>6795356</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119623701</v>
+        <v>119623971</v>
       </c>
       <c r="B17" t="n">
-        <v>91494</v>
+        <v>104994</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452000</v>
+        <v>451957</v>
       </c>
       <c r="R17" t="n">
-        <v>6795356</v>
+        <v>6795424</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119624105</v>
+        <v>119625133</v>
       </c>
       <c r="B18" t="n">
-        <v>94311</v>
+        <v>90562</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2319,38 +2329,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451926</v>
+        <v>451511</v>
       </c>
       <c r="R18" t="n">
-        <v>6795450</v>
+        <v>6795545</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,11 +2393,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Kallkällor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2414,10 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119625133</v>
+        <v>119623430</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2426,38 +2431,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451511</v>
+        <v>452010</v>
       </c>
       <c r="R19" t="n">
-        <v>6795545</v>
+        <v>6795395</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119623430</v>
+        <v>119624025</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,47 +2542,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452010</v>
+        <v>451942</v>
       </c>
       <c r="R20" t="n">
-        <v>6795395</v>
+        <v>6795447</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,10 +2632,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119624141</v>
+        <v>119625094</v>
       </c>
       <c r="B21" t="n">
-        <v>91494</v>
+        <v>90527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,34 +2648,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451909</v>
+        <v>451529</v>
       </c>
       <c r="R21" t="n">
-        <v>6795438</v>
+        <v>6795557</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2703,11 +2708,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Invid en kallkälla.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119623275</v>
+        <v>119622912</v>
       </c>
       <c r="B3" t="n">
-        <v>90334</v>
+        <v>104994</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452021</v>
+        <v>452035</v>
       </c>
       <c r="R3" t="n">
-        <v>6795414</v>
+        <v>6795377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119624110</v>
+        <v>119623275</v>
       </c>
       <c r="B4" t="n">
         <v>90334</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451915</v>
+        <v>452021</v>
       </c>
       <c r="R4" t="n">
-        <v>6795444</v>
+        <v>6795414</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119622912</v>
+        <v>119624110</v>
       </c>
       <c r="B5" t="n">
-        <v>104994</v>
+        <v>90334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452035</v>
+        <v>451915</v>
       </c>
       <c r="R5" t="n">
-        <v>6795377</v>
+        <v>6795444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119623701</v>
+        <v>119623971</v>
       </c>
       <c r="B16" t="n">
-        <v>91494</v>
+        <v>104994</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452000</v>
+        <v>451957</v>
       </c>
       <c r="R16" t="n">
-        <v>6795356</v>
+        <v>6795424</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2215,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119623971</v>
+        <v>119623701</v>
       </c>
       <c r="B17" t="n">
-        <v>104994</v>
+        <v>91494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2231,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451957</v>
+        <v>452000</v>
       </c>
       <c r="R17" t="n">
-        <v>6795424</v>
+        <v>6795356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119623805</v>
+        <v>119624582</v>
       </c>
       <c r="B2" t="n">
-        <v>94311</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451965</v>
+        <v>451684</v>
       </c>
       <c r="R2" t="n">
-        <v>6795388</v>
+        <v>6795469</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119622912</v>
+        <v>119624025</v>
       </c>
       <c r="B3" t="n">
-        <v>104994</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452035</v>
+        <v>451942</v>
       </c>
       <c r="R3" t="n">
-        <v>6795377</v>
+        <v>6795447</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119623275</v>
+        <v>119623301</v>
       </c>
       <c r="B4" t="n">
-        <v>90334</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452021</v>
+        <v>452006</v>
       </c>
       <c r="R4" t="n">
-        <v>6795414</v>
+        <v>6795400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119624110</v>
+        <v>119625963</v>
       </c>
       <c r="B5" t="n">
-        <v>90334</v>
+        <v>82305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451915</v>
+        <v>451704</v>
       </c>
       <c r="R5" t="n">
-        <v>6795444</v>
+        <v>6795497</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119624582</v>
+        <v>119624110</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>90334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451684</v>
+        <v>451915</v>
       </c>
       <c r="R6" t="n">
-        <v>6795469</v>
+        <v>6795444</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119623309</v>
+        <v>119625094</v>
       </c>
       <c r="B7" t="n">
-        <v>91494</v>
+        <v>90527</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451996</v>
+        <v>451529</v>
       </c>
       <c r="R7" t="n">
-        <v>6795413</v>
+        <v>6795557</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119623113</v>
+        <v>119622912</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>104994</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452038</v>
+        <v>452035</v>
       </c>
       <c r="R8" t="n">
-        <v>6795402</v>
+        <v>6795377</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119623199</v>
+        <v>119623805</v>
       </c>
       <c r="B9" t="n">
-        <v>90106</v>
+        <v>94311</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5754</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452026</v>
+        <v>451965</v>
       </c>
       <c r="R9" t="n">
-        <v>6795405</v>
+        <v>6795388</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119623301</v>
+        <v>119624105</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>94311</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452006</v>
+        <v>451926</v>
       </c>
       <c r="R10" t="n">
-        <v>6795400</v>
+        <v>6795450</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,6 +1567,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kallkällor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119624105</v>
+        <v>119623275</v>
       </c>
       <c r="B11" t="n">
-        <v>94311</v>
+        <v>90334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>3215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451926</v>
+        <v>452021</v>
       </c>
       <c r="R11" t="n">
-        <v>6795450</v>
+        <v>6795414</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1674,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kallkällor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119625963</v>
+        <v>119624141</v>
       </c>
       <c r="B12" t="n">
-        <v>82305</v>
+        <v>91494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,38 +1712,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451704</v>
+        <v>451909</v>
       </c>
       <c r="R12" t="n">
-        <v>6795497</v>
+        <v>6795438</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Invid en kallkälla.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119624986</v>
+        <v>119623309</v>
       </c>
       <c r="B13" t="n">
-        <v>91254</v>
+        <v>91494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,34 +1823,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451575</v>
+        <v>451996</v>
       </c>
       <c r="R13" t="n">
-        <v>6795592</v>
+        <v>6795413</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119624681</v>
+        <v>119623113</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>91494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,38 +1921,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451658</v>
+        <v>452038</v>
       </c>
       <c r="R14" t="n">
-        <v>6795526</v>
+        <v>6795402</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119624141</v>
+        <v>119624681</v>
       </c>
       <c r="B15" t="n">
-        <v>91494</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,38 +2023,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451909</v>
+        <v>451658</v>
       </c>
       <c r="R15" t="n">
-        <v>6795438</v>
+        <v>6795526</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,11 +2087,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Invid en kallkälla.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119623971</v>
+        <v>119623430</v>
       </c>
       <c r="B16" t="n">
-        <v>104994</v>
+        <v>97907</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,38 +2125,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451957</v>
+        <v>452010</v>
       </c>
       <c r="R16" t="n">
-        <v>6795424</v>
+        <v>6795395</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119623701</v>
+        <v>119623971</v>
       </c>
       <c r="B17" t="n">
-        <v>91494</v>
+        <v>104994</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,21 +2240,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2255,10 +2264,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452000</v>
+        <v>451957</v>
       </c>
       <c r="R17" t="n">
-        <v>6795356</v>
+        <v>6795424</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119623430</v>
+        <v>119624986</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>91254</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,47 +2440,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452010</v>
+        <v>451575</v>
       </c>
       <c r="R19" t="n">
-        <v>6795395</v>
+        <v>6795592</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119624025</v>
+        <v>119623199</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>90106</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5754</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451942</v>
+        <v>452026</v>
       </c>
       <c r="R20" t="n">
-        <v>6795447</v>
+        <v>6795405</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119625094</v>
+        <v>119623701</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>91494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2648,34 +2648,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451529</v>
+        <v>452000</v>
       </c>
       <c r="R21" t="n">
-        <v>6795557</v>
+        <v>6795356</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2732,6 +2732,130 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120357924</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56524</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>451903</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6795337</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2856,6 +2856,345 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120461420</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>452004</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6795386</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120461436</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57341</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>451855</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6795436</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120455163</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>452004</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6795386</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -2858,10 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120461420</v>
+        <v>120461436</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>57341</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2870,25 +2870,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2897,19 +2897,23 @@
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452004</v>
+        <v>451855</v>
       </c>
       <c r="R23" t="n">
-        <v>6795386</v>
+        <v>6795436</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120461436</v>
+        <v>120455163</v>
       </c>
       <c r="B24" t="n">
-        <v>57341</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2980,50 +2984,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451855</v>
+        <v>452004</v>
       </c>
       <c r="R24" t="n">
-        <v>6795436</v>
+        <v>6795386</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,12 +3054,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3064,6 +3068,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3082,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120455163</v>
+        <v>120461420</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3094,39 +3099,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3164,12 +3165,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3178,7 +3179,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2858,10 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120461436</v>
+        <v>120455163</v>
       </c>
       <c r="B23" t="n">
-        <v>57341</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2870,50 +2870,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100110</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451855</v>
+        <v>452004</v>
       </c>
       <c r="R23" t="n">
-        <v>6795436</v>
+        <v>6795386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2940,12 +2940,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,6 +2954,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2972,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120455163</v>
+        <v>120461420</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2984,39 +2985,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3054,12 +3051,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3068,7 +3065,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3087,10 +3083,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120461420</v>
+        <v>120461436</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>57341</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3099,25 +3095,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3126,19 +3122,23 @@
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452004</v>
+        <v>451855</v>
       </c>
       <c r="R25" t="n">
-        <v>6795386</v>
+        <v>6795436</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,6 +3194,245 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120493954</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>451990</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6795420</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120497002</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56524</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>451667</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6795441</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120493954</v>
+        <v>120497002</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>56524</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,50 +3209,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451990</v>
+        <v>451667</v>
       </c>
       <c r="R26" t="n">
-        <v>6795420</v>
+        <v>6795441</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3282,18 +3282,27 @@
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3312,10 +3321,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120497002</v>
+        <v>120493954</v>
       </c>
       <c r="B27" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3324,50 +3333,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451667</v>
+        <v>451990</v>
       </c>
       <c r="R27" t="n">
-        <v>6795441</v>
+        <v>6795420</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3397,27 +3406,18 @@
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -2973,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120461420</v>
+        <v>120461436</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>57341</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,25 +2985,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100110</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3012,19 +3012,23 @@
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452004</v>
+        <v>451855</v>
       </c>
       <c r="R24" t="n">
-        <v>6795386</v>
+        <v>6795436</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120461436</v>
+        <v>120461420</v>
       </c>
       <c r="B25" t="n">
-        <v>57341</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3095,25 +3099,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3122,23 +3126,19 @@
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451855</v>
+        <v>452004</v>
       </c>
       <c r="R25" t="n">
-        <v>6795436</v>
+        <v>6795386</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -2858,10 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120455163</v>
+        <v>120461436</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>57341</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2870,50 +2870,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100110</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452004</v>
+        <v>451855</v>
       </c>
       <c r="R23" t="n">
-        <v>6795386</v>
+        <v>6795436</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2940,12 +2940,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,7 +2954,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2973,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120461436</v>
+        <v>120461420</v>
       </c>
       <c r="B24" t="n">
-        <v>57341</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,25 +2984,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3012,23 +3011,19 @@
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451855</v>
+        <v>452004</v>
       </c>
       <c r="R24" t="n">
-        <v>6795436</v>
+        <v>6795386</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,10 +3082,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120461420</v>
+        <v>120455163</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3099,35 +3094,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3165,12 +3164,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3179,6 +3178,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120497002</v>
+        <v>120493954</v>
       </c>
       <c r="B26" t="n">
-        <v>56524</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3209,50 +3209,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451667</v>
+        <v>451990</v>
       </c>
       <c r="R26" t="n">
-        <v>6795441</v>
+        <v>6795420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3282,27 +3282,18 @@
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-19</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3321,10 +3312,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120493954</v>
+        <v>120497002</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>56524</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3333,50 +3324,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451990</v>
+        <v>451667</v>
       </c>
       <c r="R27" t="n">
-        <v>6795420</v>
+        <v>6795441</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3406,18 +3397,27 @@
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-19</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -3439,7 +3439,7 @@
         <v>121120126</v>
       </c>
       <c r="B28" t="n">
-        <v>56552</v>
+        <v>56555</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -3439,7 +3439,7 @@
         <v>121120126</v>
       </c>
       <c r="B28" t="n">
-        <v>56555</v>
+        <v>56558</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -3553,7 +3553,7 @@
         <v>122780415</v>
       </c>
       <c r="B29" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3676,6 +3676,120 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125109158</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56112</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>451891</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6795458</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -3681,7 +3681,7 @@
         <v>125109158</v>
       </c>
       <c r="B30" t="n">
-        <v>56112</v>
+        <v>56226</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3785,6 +3785,232 @@
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132477114</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56517</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>451648</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6795608</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132477046</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58109</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>451648</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6795608</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3790,7 +3790,7 @@
         <v>132477114</v>
       </c>
       <c r="B31" t="n">
-        <v>56517</v>
+        <v>56518</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>132477046</v>
       </c>
       <c r="B32" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4010,6 +4010,112 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132667638</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58384</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Övergärd, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>452007</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6795396</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3790,7 +3790,7 @@
         <v>132477114</v>
       </c>
       <c r="B31" t="n">
-        <v>56518</v>
+        <v>56522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         <v>132477046</v>
       </c>
       <c r="B32" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>132667638</v>
       </c>
       <c r="B33" t="n">
-        <v>58384</v>
+        <v>58388</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4116,6 +4116,226 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132724578</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101323</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>451910</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6795497</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132715558</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57874</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>451683</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6795451</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>132724578</v>
       </c>
       <c r="B34" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>132724578</v>
       </c>
       <c r="B34" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>132724578</v>
       </c>
       <c r="B34" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -3903,7 +3903,7 @@
         <v>132477046</v>
       </c>
       <c r="B32" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>132667638</v>
       </c>
       <c r="B33" t="n">
-        <v>58388</v>
+        <v>58389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>132724578</v>
       </c>
       <c r="B34" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>132715558</v>
       </c>
       <c r="B35" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4122,7 +4122,7 @@
         <v>132724578</v>
       </c>
       <c r="B34" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4337,6 +4337,121 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132918321</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58818</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>451860</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6795469</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4122,7 +4122,7 @@
         <v>132724578</v>
       </c>
       <c r="B34" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3093,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120357924</v>
+        <v>135260102</v>
       </c>
       <c r="B26" t="n">
-        <v>57132</v>
+        <v>57162</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,49 +3104,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451903</v>
+        <v>451568</v>
       </c>
       <c r="R26" t="n">
-        <v>6795337</v>
+        <v>6795589</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3170,22 +3163,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3200,19 +3198,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120497002</v>
+        <v>120357924</v>
       </c>
       <c r="B27" t="n">
         <v>57132</v>
@@ -3246,23 +3244,23 @@
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451667</v>
+        <v>451903</v>
       </c>
       <c r="R27" t="n">
-        <v>6795441</v>
+        <v>6795337</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3289,22 +3287,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3331,7 +3329,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121120126</v>
+        <v>120497002</v>
       </c>
       <c r="B28" t="n">
         <v>57132</v>
@@ -3365,23 +3363,23 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>451990</v>
+        <v>451667</v>
       </c>
       <c r="R28" t="n">
-        <v>6795420</v>
+        <v>6795441</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3408,12 +3406,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3440,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134519429</v>
+        <v>121120126</v>
       </c>
       <c r="B29" t="n">
-        <v>57153</v>
+        <v>57132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3468,25 +3476,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451845</v>
+        <v>451990</v>
       </c>
       <c r="R29" t="n">
-        <v>6795506</v>
+        <v>6795420</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3510,22 +3525,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3540,69 +3545,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132667638</v>
+        <v>134519429</v>
       </c>
       <c r="B30" t="n">
-        <v>58410</v>
+        <v>57153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103001</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Övergärd, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452007</v>
+        <v>451845</v>
       </c>
       <c r="R30" t="n">
-        <v>6795396</v>
+        <v>6795506</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3626,12 +3627,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3658,35 +3669,39 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133881550</v>
+        <v>132667638</v>
       </c>
       <c r="B31" t="n">
-        <v>58349</v>
+        <v>58410</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3694,17 +3709,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451505</v>
+        <v>452007</v>
       </c>
       <c r="R31" t="n">
-        <v>6795559</v>
+        <v>6795396</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3728,22 +3743,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3770,61 +3775,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122780415</v>
+        <v>133881550</v>
       </c>
       <c r="B32" t="n">
-        <v>58114</v>
+        <v>58349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451903</v>
+        <v>451505</v>
       </c>
       <c r="R32" t="n">
-        <v>6795337</v>
+        <v>6795559</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,22 +3845,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3881,22 +3875,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132477046</v>
+        <v>122780415</v>
       </c>
       <c r="B33" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3923,14 +3917,14 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3944,13 +3938,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451648</v>
+        <v>451903</v>
       </c>
       <c r="R33" t="n">
-        <v>6795608</v>
+        <v>6795337</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3974,12 +3968,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4006,7 +4010,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134471194</v>
+        <v>132477046</v>
       </c>
       <c r="B34" t="n">
         <v>58136</v>
@@ -4034,7 +4038,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
@@ -4042,20 +4050,24 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451635</v>
+        <v>451648</v>
       </c>
       <c r="R34" t="n">
-        <v>6795544</v>
+        <v>6795608</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4079,12 +4091,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4111,60 +4123,56 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132477079</v>
+        <v>134471194</v>
       </c>
       <c r="B35" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451648</v>
+        <v>451635</v>
       </c>
       <c r="R35" t="n">
-        <v>6795608</v>
+        <v>6795544</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4188,12 +4196,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4220,60 +4228,60 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125109158</v>
+        <v>132477079</v>
       </c>
       <c r="B36" t="n">
-        <v>56522</v>
+        <v>58131</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>206004</v>
+        <v>103023</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451891</v>
+        <v>451648</v>
       </c>
       <c r="R36" t="n">
-        <v>6795458</v>
+        <v>6795608</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4297,12 +4305,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4329,10 +4337,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132477114</v>
+        <v>125109158</v>
       </c>
       <c r="B37" t="n">
-        <v>56539</v>
+        <v>56522</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4369,24 +4377,20 @@
           <t>gående/springande</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451648</v>
+        <v>451891</v>
       </c>
       <c r="R37" t="n">
-        <v>6795608</v>
+        <v>6795458</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4410,12 +4414,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4442,27 +4446,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132918321</v>
+        <v>132477114</v>
       </c>
       <c r="B38" t="n">
-        <v>58839</v>
+        <v>56539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4472,15 +4476,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4494,13 +4497,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451860</v>
+        <v>451648</v>
       </c>
       <c r="R38" t="n">
-        <v>6795469</v>
+        <v>6795608</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4524,12 +4527,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4538,7 +4541,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4557,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134446393</v>
+        <v>132918321</v>
       </c>
       <c r="B39" t="n">
-        <v>99103</v>
+        <v>58839</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,45 +4570,54 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219788</v>
+        <v>208249</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>451856</v>
+        <v>451860</v>
       </c>
       <c r="R39" t="n">
-        <v>6795459</v>
+        <v>6795469</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4630,12 +4641,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4663,10 +4674,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133997108</v>
+        <v>134446393</v>
       </c>
       <c r="B40" t="n">
-        <v>99112</v>
+        <v>99103</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4674,16 +4685,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4693,22 +4704,26 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451891</v>
+        <v>451856</v>
       </c>
       <c r="R40" t="n">
-        <v>6795458</v>
+        <v>6795459</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4732,12 +4747,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4765,7 +4780,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133997151</v>
+        <v>133997108</v>
       </c>
       <c r="B41" t="n">
         <v>99112</v>
@@ -4800,17 +4815,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451900</v>
+        <v>451891</v>
       </c>
       <c r="R41" t="n">
-        <v>6795487</v>
+        <v>6795458</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4867,7 +4882,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134446465</v>
+        <v>133997151</v>
       </c>
       <c r="B42" t="n">
         <v>99112</v>
@@ -4897,23 +4912,19 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451867</v>
+        <v>451900</v>
       </c>
       <c r="R42" t="n">
-        <v>6795467</v>
+        <v>6795487</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4940,12 +4951,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4973,7 +4984,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134452196</v>
+        <v>134446465</v>
       </c>
       <c r="B43" t="n">
         <v>99112</v>
@@ -5003,7 +5014,11 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
@@ -5012,10 +5027,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451858</v>
+        <v>451867</v>
       </c>
       <c r="R43" t="n">
-        <v>6795529</v>
+        <v>6795467</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5075,7 +5090,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134452278</v>
+        <v>134452196</v>
       </c>
       <c r="B44" t="n">
         <v>99112</v>
@@ -5114,7 +5129,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451878</v>
+        <v>451858</v>
       </c>
       <c r="R44" t="n">
         <v>6795529</v>
@@ -5177,7 +5192,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134452340</v>
+        <v>134452278</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5216,10 +5231,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451934</v>
+        <v>451878</v>
       </c>
       <c r="R45" t="n">
-        <v>6795489</v>
+        <v>6795529</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5279,7 +5294,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134452392</v>
+        <v>134452340</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5318,10 +5333,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451845</v>
+        <v>451934</v>
       </c>
       <c r="R46" t="n">
-        <v>6795346</v>
+        <v>6795489</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5381,7 +5396,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134452446</v>
+        <v>134452392</v>
       </c>
       <c r="B47" t="n">
         <v>99112</v>
@@ -5420,10 +5435,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451876</v>
+        <v>451845</v>
       </c>
       <c r="R47" t="n">
-        <v>6795437</v>
+        <v>6795346</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5483,7 +5498,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134452468</v>
+        <v>134452446</v>
       </c>
       <c r="B48" t="n">
         <v>99112</v>
@@ -5522,10 +5537,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451872</v>
+        <v>451876</v>
       </c>
       <c r="R48" t="n">
-        <v>6795459</v>
+        <v>6795437</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5585,7 +5600,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134470975</v>
+        <v>134452468</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -5613,33 +5628,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451828</v>
+        <v>451872</v>
       </c>
       <c r="R49" t="n">
-        <v>6795362</v>
+        <v>6795459</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5666,12 +5669,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5699,7 +5702,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134471030</v>
+        <v>134470975</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -5727,21 +5730,33 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451822</v>
+        <v>451828</v>
       </c>
       <c r="R50" t="n">
-        <v>6795403</v>
+        <v>6795362</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5801,7 +5816,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134471064</v>
+        <v>134471030</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -5840,10 +5855,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451754</v>
+        <v>451822</v>
       </c>
       <c r="R51" t="n">
-        <v>6795474</v>
+        <v>6795403</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5903,7 +5918,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134471377</v>
+        <v>134471064</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -5942,10 +5957,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451524</v>
+        <v>451754</v>
       </c>
       <c r="R52" t="n">
-        <v>6795576</v>
+        <v>6795474</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6005,7 +6020,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134519430</v>
+        <v>134471377</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6034,19 +6049,23 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451846</v>
+        <v>451524</v>
       </c>
       <c r="R53" t="n">
-        <v>6795506</v>
+        <v>6795576</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6070,22 +6089,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6094,25 +6103,26 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135087727</v>
+        <v>134519430</v>
       </c>
       <c r="B54" t="n">
         <v>99112</v>
@@ -6141,23 +6151,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451853</v>
+        <v>451846</v>
       </c>
       <c r="R54" t="n">
-        <v>6795315</v>
+        <v>6795506</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6181,12 +6187,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6195,29 +6211,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134446457</v>
+        <v>135087727</v>
       </c>
       <c r="B55" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6225,42 +6240,38 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451867</v>
+        <v>451853</v>
       </c>
       <c r="R55" t="n">
-        <v>6795467</v>
+        <v>6795315</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6287,12 +6298,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6320,7 +6331,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134452308</v>
+        <v>134446457</v>
       </c>
       <c r="B56" t="n">
         <v>99099</v>
@@ -6363,10 +6374,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451924</v>
+        <v>451867</v>
       </c>
       <c r="R56" t="n">
-        <v>6795490</v>
+        <v>6795467</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6426,7 +6437,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134471116</v>
+        <v>134452308</v>
       </c>
       <c r="B57" t="n">
         <v>99099</v>
@@ -6456,7 +6467,11 @@
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6465,10 +6480,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451657</v>
+        <v>451924</v>
       </c>
       <c r="R57" t="n">
-        <v>6795504</v>
+        <v>6795490</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6495,12 +6510,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6528,7 +6543,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134471163</v>
+        <v>134471116</v>
       </c>
       <c r="B58" t="n">
         <v>99099</v>
@@ -6567,10 +6582,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451656</v>
+        <v>451657</v>
       </c>
       <c r="R58" t="n">
-        <v>6795514</v>
+        <v>6795504</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6630,7 +6645,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134471374</v>
+        <v>134471163</v>
       </c>
       <c r="B59" t="n">
         <v>99099</v>
@@ -6669,10 +6684,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451524</v>
+        <v>451656</v>
       </c>
       <c r="R59" t="n">
-        <v>6795576</v>
+        <v>6795514</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6732,10 +6747,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134471215</v>
+        <v>134471374</v>
       </c>
       <c r="B60" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6743,21 +6758,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6767,14 +6782,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451641</v>
+        <v>451524</v>
       </c>
       <c r="R60" t="n">
-        <v>6795575</v>
+        <v>6795576</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6834,7 +6849,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134471223</v>
+        <v>134471215</v>
       </c>
       <c r="B61" t="n">
         <v>108274</v>
@@ -6869,14 +6884,14 @@
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451640</v>
+        <v>451641</v>
       </c>
       <c r="R61" t="n">
-        <v>6795589</v>
+        <v>6795575</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6936,7 +6951,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134471252</v>
+        <v>134471223</v>
       </c>
       <c r="B62" t="n">
         <v>108274</v>
@@ -6975,10 +6990,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>451628</v>
+        <v>451640</v>
       </c>
       <c r="R62" t="n">
-        <v>6795600</v>
+        <v>6795589</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7038,54 +7053,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119623430</v>
+        <v>134471252</v>
       </c>
       <c r="B63" t="n">
-        <v>99118</v>
+        <v>108274</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452010</v>
+        <v>451628</v>
       </c>
       <c r="R63" t="n">
-        <v>6795395</v>
+        <v>6795600</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7112,12 +7122,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7126,25 +7136,26 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120455163</v>
+        <v>119623430</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -7174,7 +7185,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7182,19 +7193,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452004</v>
+        <v>452010</v>
       </c>
       <c r="R64" t="n">
-        <v>6795386</v>
+        <v>6795395</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7221,12 +7229,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7235,26 +7243,25 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120493954</v>
+        <v>120455163</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -7284,7 +7291,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7297,14 +7304,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451990</v>
+        <v>452004</v>
       </c>
       <c r="R65" t="n">
-        <v>6795420</v>
+        <v>6795386</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7331,12 +7338,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7364,10 +7371,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133997095</v>
+        <v>120493954</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7394,12 +7401,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -7407,14 +7414,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>451903</v>
+        <v>451990</v>
       </c>
       <c r="R66" t="n">
-        <v>6795472</v>
+        <v>6795420</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7441,12 +7448,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7474,7 +7481,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133997219</v>
+        <v>133997095</v>
       </c>
       <c r="B67" t="n">
         <v>99195</v>
@@ -7504,7 +7511,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7521,10 +7528,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451888</v>
+        <v>451903</v>
       </c>
       <c r="R67" t="n">
-        <v>6795475</v>
+        <v>6795472</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7584,45 +7591,57 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119622912</v>
+        <v>133997219</v>
       </c>
       <c r="B68" t="n">
-        <v>106229</v>
+        <v>99195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452035</v>
+        <v>451888</v>
       </c>
       <c r="R68" t="n">
-        <v>6795377</v>
+        <v>6795475</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7649,12 +7668,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7663,25 +7682,26 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119623971</v>
+        <v>119622912</v>
       </c>
       <c r="B69" t="n">
         <v>106229</v>
@@ -7716,10 +7736,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>451957</v>
+        <v>452035</v>
       </c>
       <c r="R69" t="n">
-        <v>6795424</v>
+        <v>6795377</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7778,10 +7798,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134452234</v>
+        <v>119623971</v>
       </c>
       <c r="B70" t="n">
-        <v>98060</v>
+        <v>106229</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7789,38 +7809,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>451878</v>
+        <v>451957</v>
       </c>
       <c r="R70" t="n">
-        <v>6795529</v>
+        <v>6795424</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7847,12 +7863,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7861,26 +7877,25 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134452406</v>
+        <v>134452234</v>
       </c>
       <c r="B71" t="n">
         <v>98060</v>
@@ -7919,10 +7934,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>451858</v>
+        <v>451878</v>
       </c>
       <c r="R71" t="n">
-        <v>6795410</v>
+        <v>6795529</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7982,7 +7997,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134452426</v>
+        <v>134452406</v>
       </c>
       <c r="B72" t="n">
         <v>98060</v>
@@ -8021,10 +8036,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>451875</v>
+        <v>451858</v>
       </c>
       <c r="R72" t="n">
-        <v>6795422</v>
+        <v>6795410</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8084,7 +8099,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134519426</v>
+        <v>134452426</v>
       </c>
       <c r="B73" t="n">
         <v>98060</v>
@@ -8113,19 +8128,23 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>451669</v>
+        <v>451875</v>
       </c>
       <c r="R73" t="n">
-        <v>6795570</v>
+        <v>6795422</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8149,22 +8168,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8173,28 +8182,29 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134470979</v>
+        <v>134519426</v>
       </c>
       <c r="B74" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8202,41 +8212,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>451828</v>
+        <v>451669</v>
       </c>
       <c r="R74" t="n">
-        <v>6795362</v>
+        <v>6795570</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8260,12 +8266,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8274,26 +8290,25 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134471102</v>
+        <v>134470979</v>
       </c>
       <c r="B75" t="n">
         <v>99217</v>
@@ -8328,14 +8343,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>451693</v>
+        <v>451828</v>
       </c>
       <c r="R75" t="n">
-        <v>6795486</v>
+        <v>6795362</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8395,7 +8410,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134471378</v>
+        <v>134471102</v>
       </c>
       <c r="B76" t="n">
         <v>99217</v>
@@ -8434,10 +8449,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>451524</v>
+        <v>451693</v>
       </c>
       <c r="R76" t="n">
-        <v>6795576</v>
+        <v>6795486</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8497,10 +8512,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132724578</v>
+        <v>134471378</v>
       </c>
       <c r="B77" t="n">
-        <v>101403</v>
+        <v>99217</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8508,57 +8523,41 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>451910</v>
+        <v>451524</v>
       </c>
       <c r="R77" t="n">
-        <v>6795497</v>
+        <v>6795576</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8582,12 +8581,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8612,6 +8611,124 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132724578</v>
+      </c>
+      <c r="B78" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>451910</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6795497</v>
+      </c>
+      <c r="S78" t="n">
+        <v>25</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2237,53 +2237,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132715558</v>
+        <v>135370442</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451683</v>
+        <v>451697</v>
       </c>
       <c r="R18" t="n">
-        <v>6795451</v>
+        <v>6795538</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2307,12 +2305,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2321,71 +2319,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120461420</v>
+        <v>135374857</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452004</v>
+        <v>451506</v>
       </c>
       <c r="R19" t="n">
-        <v>6795386</v>
+        <v>6795579</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2412,12 +2406,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,6 +2420,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2444,53 +2439,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133881553</v>
+        <v>135374874</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451678</v>
+        <v>451511</v>
       </c>
       <c r="R20" t="n">
-        <v>6795601</v>
+        <v>6795591</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2514,27 +2507,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Levande gran</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,45 +2521,46 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134471421</v>
+        <v>132715558</v>
       </c>
       <c r="B21" t="n">
-        <v>57972</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2590,27 +2569,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451503</v>
+        <v>451683</v>
       </c>
       <c r="R21" t="n">
-        <v>6795552</v>
+        <v>6795451</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2634,12 +2610,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2654,22 +2630,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134471435</v>
+        <v>120461420</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2694,25 +2670,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451506</v>
+        <v>452004</v>
       </c>
       <c r="R22" t="n">
-        <v>6795602</v>
+        <v>6795386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,12 +2715,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2771,7 +2747,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134519427</v>
+        <v>133881553</v>
       </c>
       <c r="B23" t="n">
         <v>57972</v>
@@ -2807,14 +2783,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451819</v>
+        <v>451678</v>
       </c>
       <c r="R23" t="n">
-        <v>6795533</v>
+        <v>6795601</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2841,22 +2817,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Levande gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2883,10 +2864,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120461436</v>
+        <v>134471421</v>
       </c>
       <c r="B24" t="n">
-        <v>57945</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2894,46 +2875,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451855</v>
+        <v>451503</v>
       </c>
       <c r="R24" t="n">
-        <v>6795436</v>
+        <v>6795552</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2960,12 +2937,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2992,38 +2969,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132752338</v>
+        <v>134471435</v>
       </c>
       <c r="B25" t="n">
-        <v>57835</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100136</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3031,13 +3012,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451810</v>
+        <v>451506</v>
       </c>
       <c r="R25" t="n">
-        <v>6795373</v>
+        <v>6795602</v>
       </c>
       <c r="S25" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3061,12 +3042,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3081,22 +3062,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135260102</v>
+        <v>134519427</v>
       </c>
       <c r="B26" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,39 +3085,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451568</v>
+        <v>451819</v>
       </c>
       <c r="R26" t="n">
-        <v>6795589</v>
+        <v>6795533</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3163,27 +3144,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3210,10 +3186,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120357924</v>
+        <v>120461436</v>
       </c>
       <c r="B27" t="n">
-        <v>57132</v>
+        <v>57945</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,35 +3197,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>100110</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3257,10 +3233,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451903</v>
+        <v>451855</v>
       </c>
       <c r="R27" t="n">
-        <v>6795337</v>
+        <v>6795436</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3287,22 +3263,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3329,45 +3295,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120497002</v>
+        <v>132752338</v>
       </c>
       <c r="B28" t="n">
-        <v>57132</v>
+        <v>57835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>100136</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -3376,13 +3334,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>451667</v>
+        <v>451810</v>
       </c>
       <c r="R28" t="n">
-        <v>6795441</v>
+        <v>6795373</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3406,22 +3364,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3436,22 +3384,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121120126</v>
+        <v>135260102</v>
       </c>
       <c r="B29" t="n">
-        <v>57132</v>
+        <v>57162</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,49 +3407,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451990</v>
+        <v>451568</v>
       </c>
       <c r="R29" t="n">
-        <v>6795420</v>
+        <v>6795589</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3525,12 +3466,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3545,22 +3501,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134519429</v>
+        <v>120357924</v>
       </c>
       <c r="B30" t="n">
-        <v>57153</v>
+        <v>57132</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3585,25 +3541,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451845</v>
+        <v>451903</v>
       </c>
       <c r="R30" t="n">
-        <v>6795506</v>
+        <v>6795337</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3627,22 +3590,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-10-12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3657,69 +3620,72 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132667638</v>
+        <v>120497002</v>
       </c>
       <c r="B31" t="n">
-        <v>58410</v>
+        <v>57132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103001</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452007</v>
+        <v>451667</v>
       </c>
       <c r="R31" t="n">
-        <v>6795396</v>
+        <v>6795441</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3743,12 +3709,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3763,22 +3739,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133881550</v>
+        <v>121120126</v>
       </c>
       <c r="B32" t="n">
-        <v>58349</v>
+        <v>57132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3786,16 +3762,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3803,22 +3779,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451505</v>
+        <v>451990</v>
       </c>
       <c r="R32" t="n">
-        <v>6795559</v>
+        <v>6795420</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3845,22 +3828,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3875,76 +3848,65 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122780415</v>
+        <v>134519429</v>
       </c>
       <c r="B33" t="n">
-        <v>58114</v>
+        <v>57153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451903</v>
+        <v>451845</v>
       </c>
       <c r="R33" t="n">
-        <v>6795337</v>
+        <v>6795506</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3968,22 +3930,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,22 +3960,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132477046</v>
+        <v>132667638</v>
       </c>
       <c r="B34" t="n">
-        <v>58136</v>
+        <v>58410</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4021,21 +3983,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4043,31 +4005,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451648</v>
+        <v>452007</v>
       </c>
       <c r="R34" t="n">
-        <v>6795608</v>
+        <v>6795396</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4091,12 +4046,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4111,65 +4066,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134471194</v>
+        <v>133881550</v>
       </c>
       <c r="B35" t="n">
-        <v>58136</v>
+        <v>58349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451635</v>
+        <v>451505</v>
       </c>
       <c r="R35" t="n">
-        <v>6795544</v>
+        <v>6795559</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4196,12 +4148,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4216,44 +4178,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132477079</v>
+        <v>122780415</v>
       </c>
       <c r="B36" t="n">
-        <v>58131</v>
+        <v>58114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4263,7 +4225,11 @@
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4275,13 +4241,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451648</v>
+        <v>451903</v>
       </c>
       <c r="R36" t="n">
-        <v>6795608</v>
+        <v>6795337</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4305,12 +4271,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4337,10 +4313,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125109158</v>
+        <v>132477046</v>
       </c>
       <c r="B37" t="n">
-        <v>56522</v>
+        <v>58136</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4348,21 +4324,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4374,23 +4350,27 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451891</v>
+        <v>451648</v>
       </c>
       <c r="R37" t="n">
-        <v>6795458</v>
+        <v>6795608</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4414,12 +4394,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4446,10 +4426,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132477114</v>
+        <v>134471194</v>
       </c>
       <c r="B38" t="n">
-        <v>56539</v>
+        <v>58136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,53 +4437,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451648</v>
+        <v>451635</v>
       </c>
       <c r="R38" t="n">
-        <v>6795608</v>
+        <v>6795544</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4527,12 +4499,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4559,10 +4531,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132918321</v>
+        <v>132477079</v>
       </c>
       <c r="B39" t="n">
-        <v>58839</v>
+        <v>58131</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4570,36 +4542,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208249</v>
+        <v>103023</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4611,13 +4578,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>451860</v>
+        <v>451648</v>
       </c>
       <c r="R39" t="n">
-        <v>6795469</v>
+        <v>6795608</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4641,12 +4608,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4655,7 +4622,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4674,56 +4640,60 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134446393</v>
+        <v>125109158</v>
       </c>
       <c r="B40" t="n">
-        <v>99103</v>
+        <v>56522</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219788</v>
+        <v>206004</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451856</v>
+        <v>451891</v>
       </c>
       <c r="R40" t="n">
-        <v>6795459</v>
+        <v>6795458</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4747,12 +4717,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4761,7 +4731,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4780,52 +4749,64 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133997108</v>
+        <v>132477114</v>
       </c>
       <c r="B41" t="n">
-        <v>99112</v>
+        <v>56539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>206004</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451891</v>
+        <v>451648</v>
       </c>
       <c r="R41" t="n">
-        <v>6795458</v>
+        <v>6795608</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4849,12 +4830,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4863,7 +4844,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4882,10 +4862,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133997151</v>
+        <v>132918321</v>
       </c>
       <c r="B42" t="n">
-        <v>99112</v>
+        <v>58839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4893,41 +4873,54 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451900</v>
+        <v>451860</v>
       </c>
       <c r="R42" t="n">
-        <v>6795487</v>
+        <v>6795469</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4951,12 +4944,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4984,10 +4977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134446465</v>
+        <v>134446393</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>99103</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4995,16 +4988,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5023,14 +5016,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451867</v>
+        <v>451856</v>
       </c>
       <c r="R43" t="n">
-        <v>6795467</v>
+        <v>6795459</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5090,7 +5083,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134452196</v>
+        <v>133997108</v>
       </c>
       <c r="B44" t="n">
         <v>99112</v>
@@ -5129,13 +5122,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451858</v>
+        <v>451891</v>
       </c>
       <c r="R44" t="n">
-        <v>6795529</v>
+        <v>6795458</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5159,12 +5152,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5192,7 +5185,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134452278</v>
+        <v>133997151</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5227,14 +5220,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451878</v>
+        <v>451900</v>
       </c>
       <c r="R45" t="n">
-        <v>6795529</v>
+        <v>6795487</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5261,12 +5254,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5294,7 +5287,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134452340</v>
+        <v>134446465</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5324,7 +5317,11 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -5333,10 +5330,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451934</v>
+        <v>451867</v>
       </c>
       <c r="R46" t="n">
-        <v>6795489</v>
+        <v>6795467</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5396,7 +5393,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134452392</v>
+        <v>134452196</v>
       </c>
       <c r="B47" t="n">
         <v>99112</v>
@@ -5435,10 +5432,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451845</v>
+        <v>451858</v>
       </c>
       <c r="R47" t="n">
-        <v>6795346</v>
+        <v>6795529</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5498,7 +5495,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134452446</v>
+        <v>134452278</v>
       </c>
       <c r="B48" t="n">
         <v>99112</v>
@@ -5537,10 +5534,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451876</v>
+        <v>451878</v>
       </c>
       <c r="R48" t="n">
-        <v>6795437</v>
+        <v>6795529</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5600,7 +5597,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134452468</v>
+        <v>134452340</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -5639,10 +5636,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451872</v>
+        <v>451934</v>
       </c>
       <c r="R49" t="n">
-        <v>6795459</v>
+        <v>6795489</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5702,7 +5699,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134470975</v>
+        <v>134452392</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -5730,33 +5727,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451828</v>
+        <v>451845</v>
       </c>
       <c r="R50" t="n">
-        <v>6795362</v>
+        <v>6795346</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5783,12 +5768,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5816,7 +5801,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134471030</v>
+        <v>134452446</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -5855,10 +5840,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451822</v>
+        <v>451876</v>
       </c>
       <c r="R51" t="n">
-        <v>6795403</v>
+        <v>6795437</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5885,12 +5870,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5918,7 +5903,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134471064</v>
+        <v>134452468</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -5957,10 +5942,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451754</v>
+        <v>451872</v>
       </c>
       <c r="R52" t="n">
-        <v>6795474</v>
+        <v>6795459</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5987,12 +5972,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6020,7 +6005,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134471377</v>
+        <v>134470975</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6048,21 +6033,33 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451524</v>
+        <v>451828</v>
       </c>
       <c r="R53" t="n">
-        <v>6795576</v>
+        <v>6795362</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6122,7 +6119,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134519430</v>
+        <v>134471030</v>
       </c>
       <c r="B54" t="n">
         <v>99112</v>
@@ -6151,19 +6148,23 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451846</v>
+        <v>451822</v>
       </c>
       <c r="R54" t="n">
-        <v>6795506</v>
+        <v>6795403</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6187,22 +6188,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6211,25 +6202,26 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135087727</v>
+        <v>134471064</v>
       </c>
       <c r="B55" t="n">
         <v>99112</v>
@@ -6264,14 +6256,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451853</v>
+        <v>451754</v>
       </c>
       <c r="R55" t="n">
-        <v>6795315</v>
+        <v>6795474</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6298,12 +6290,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6331,10 +6323,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134446457</v>
+        <v>134471377</v>
       </c>
       <c r="B56" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6342,30 +6334,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -6374,10 +6362,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451867</v>
+        <v>451524</v>
       </c>
       <c r="R56" t="n">
-        <v>6795467</v>
+        <v>6795576</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6404,12 +6392,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6437,10 +6425,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134452308</v>
+        <v>134519430</v>
       </c>
       <c r="B57" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6448,45 +6436,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451924</v>
+        <v>451846</v>
       </c>
       <c r="R57" t="n">
-        <v>6795490</v>
+        <v>6795506</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6510,12 +6490,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6524,29 +6514,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134471116</v>
+        <v>135087727</v>
       </c>
       <c r="B58" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6554,21 +6543,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6578,14 +6567,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451657</v>
+        <v>451853</v>
       </c>
       <c r="R58" t="n">
-        <v>6795504</v>
+        <v>6795315</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6612,12 +6601,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6645,10 +6634,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134471163</v>
+        <v>135370390</v>
       </c>
       <c r="B59" t="n">
-        <v>99099</v>
+        <v>99094</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6656,38 +6645,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220093</v>
+        <v>219795</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451656</v>
+        <v>451924</v>
       </c>
       <c r="R59" t="n">
-        <v>6795514</v>
+        <v>6795456</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6714,12 +6707,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I källmiljö</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6747,10 +6745,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134471374</v>
+        <v>135384823</v>
       </c>
       <c r="B60" t="n">
-        <v>99099</v>
+        <v>108205</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6758,21 +6756,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220093</v>
+        <v>220083</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6786,10 +6784,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451524</v>
+        <v>451640</v>
       </c>
       <c r="R60" t="n">
-        <v>6795576</v>
+        <v>6795589</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6816,12 +6814,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Invid källbäck</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6849,10 +6852,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134471215</v>
+        <v>134446457</v>
       </c>
       <c r="B61" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6860,38 +6863,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451641</v>
+        <v>451867</v>
       </c>
       <c r="R61" t="n">
-        <v>6795575</v>
+        <v>6795467</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6918,12 +6925,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6951,10 +6958,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134471223</v>
+        <v>134452308</v>
       </c>
       <c r="B62" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6962,26 +6969,30 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -6990,10 +7001,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>451640</v>
+        <v>451924</v>
       </c>
       <c r="R62" t="n">
-        <v>6795589</v>
+        <v>6795490</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7020,12 +7031,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7053,10 +7064,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134471252</v>
+        <v>134471116</v>
       </c>
       <c r="B63" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7064,21 +7075,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7092,10 +7103,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>451628</v>
+        <v>451657</v>
       </c>
       <c r="R63" t="n">
-        <v>6795600</v>
+        <v>6795504</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7155,54 +7166,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119623430</v>
+        <v>134471163</v>
       </c>
       <c r="B64" t="n">
-        <v>99118</v>
+        <v>99099</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452010</v>
+        <v>451656</v>
       </c>
       <c r="R64" t="n">
-        <v>6795395</v>
+        <v>6795514</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7229,12 +7235,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7243,75 +7249,68 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120455163</v>
+        <v>134471374</v>
       </c>
       <c r="B65" t="n">
-        <v>99118</v>
+        <v>99099</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452004</v>
+        <v>451524</v>
       </c>
       <c r="R65" t="n">
-        <v>6795386</v>
+        <v>6795576</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7338,12 +7337,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7371,57 +7370,49 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120493954</v>
+        <v>134471215</v>
       </c>
       <c r="B66" t="n">
-        <v>99118</v>
+        <v>108274</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>451990</v>
+        <v>451641</v>
       </c>
       <c r="R66" t="n">
-        <v>6795420</v>
+        <v>6795575</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7448,12 +7439,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7481,57 +7472,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133997095</v>
+        <v>134471223</v>
       </c>
       <c r="B67" t="n">
-        <v>99195</v>
+        <v>108274</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451903</v>
+        <v>451640</v>
       </c>
       <c r="R67" t="n">
-        <v>6795472</v>
+        <v>6795589</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7558,12 +7541,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7591,57 +7574,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133997219</v>
+        <v>134471252</v>
       </c>
       <c r="B68" t="n">
-        <v>99195</v>
+        <v>108274</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>451888</v>
+        <v>451628</v>
       </c>
       <c r="R68" t="n">
-        <v>6795475</v>
+        <v>6795600</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7668,12 +7643,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7701,45 +7676,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119622912</v>
+        <v>119623430</v>
       </c>
       <c r="B69" t="n">
-        <v>106229</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452035</v>
+        <v>452010</v>
       </c>
       <c r="R69" t="n">
-        <v>6795377</v>
+        <v>6795395</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7798,45 +7782,57 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119623971</v>
+        <v>120455163</v>
       </c>
       <c r="B70" t="n">
-        <v>106229</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>451957</v>
+        <v>452004</v>
       </c>
       <c r="R70" t="n">
-        <v>6795424</v>
+        <v>6795386</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7863,12 +7859,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7877,67 +7873,76 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134452234</v>
+        <v>120493954</v>
       </c>
       <c r="B71" t="n">
-        <v>98060</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>451878</v>
+        <v>451990</v>
       </c>
       <c r="R71" t="n">
-        <v>6795529</v>
+        <v>6795420</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7964,12 +7969,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7997,49 +8002,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134452406</v>
+        <v>133997095</v>
       </c>
       <c r="B72" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>451858</v>
+        <v>451903</v>
       </c>
       <c r="R72" t="n">
-        <v>6795410</v>
+        <v>6795472</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8066,12 +8079,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8099,49 +8112,57 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134452426</v>
+        <v>133997219</v>
       </c>
       <c r="B73" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>451875</v>
+        <v>451888</v>
       </c>
       <c r="R73" t="n">
-        <v>6795422</v>
+        <v>6795475</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8168,12 +8189,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8201,10 +8222,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134519426</v>
+        <v>119622912</v>
       </c>
       <c r="B74" t="n">
-        <v>98060</v>
+        <v>106229</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8212,37 +8233,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>451669</v>
+        <v>452035</v>
       </c>
       <c r="R74" t="n">
-        <v>6795570</v>
+        <v>6795377</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8266,22 +8287,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8296,22 +8307,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134470979</v>
+        <v>119623971</v>
       </c>
       <c r="B75" t="n">
-        <v>99217</v>
+        <v>106229</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8319,38 +8330,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>451828</v>
+        <v>451957</v>
       </c>
       <c r="R75" t="n">
-        <v>6795362</v>
+        <v>6795424</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8377,12 +8384,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8391,29 +8398,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134471102</v>
+        <v>134452234</v>
       </c>
       <c r="B76" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8421,21 +8427,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8449,10 +8455,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>451693</v>
+        <v>451878</v>
       </c>
       <c r="R76" t="n">
-        <v>6795486</v>
+        <v>6795529</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8479,12 +8485,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8512,10 +8518,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134471378</v>
+        <v>134452406</v>
       </c>
       <c r="B77" t="n">
-        <v>99217</v>
+        <v>98060</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8523,21 +8529,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8551,10 +8557,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>451524</v>
+        <v>451858</v>
       </c>
       <c r="R77" t="n">
-        <v>6795576</v>
+        <v>6795410</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8581,12 +8587,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8614,10 +8620,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132724578</v>
+        <v>134452426</v>
       </c>
       <c r="B78" t="n">
-        <v>101403</v>
+        <v>98060</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8625,57 +8631,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>451910</v>
+        <v>451875</v>
       </c>
       <c r="R78" t="n">
-        <v>6795497</v>
+        <v>6795422</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8699,12 +8689,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8729,6 +8719,741 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>134519426</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Käsdajk-Övergärd, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>451669</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6795570</v>
+      </c>
+      <c r="S79" t="n">
+        <v>8</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135370746</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>451924</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6795456</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135370757</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>451910</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6795497</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>134470979</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>451828</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6795362</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>134471102</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>451693</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6795486</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134471378</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>451524</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6795576</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132724578</v>
+      </c>
+      <c r="B85" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>451910</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6795497</v>
+      </c>
+      <c r="S85" t="n">
+        <v>25</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AZ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625133</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625963</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119623805</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624105</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119623275</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624110</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624986</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119623113</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119623309</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119623701</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624141</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625094</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119623199</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119623301</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119624582</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2335,6 +2420,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370442</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135374857</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2537,6 +2632,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135374874</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2639,6 +2739,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132715558</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2744,6 +2849,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461420</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2861,6 +2971,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133881553</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2966,6 +3081,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471421</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3071,6 +3191,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471435</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3183,6 +3308,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134519427</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3292,6 +3422,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120461436</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3393,6 +3528,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132752338</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3510,6 +3650,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135260102</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3629,6 +3774,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120357924</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3748,6 +3898,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120497002</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3857,6 +4012,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121120126</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3969,6 +4129,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134519429</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4075,6 +4240,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132667638</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4187,6 +4357,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133881550</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4310,6 +4485,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122780415</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4423,6 +4603,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132477046</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4528,6 +4713,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471194</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4637,6 +4827,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132477079</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4746,6 +4941,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125109158</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4859,6 +5059,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132477114</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4974,6 +5179,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132918321</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5080,6 +5290,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446393</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5182,6 +5397,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133997108</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5284,6 +5504,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133997151</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5390,6 +5615,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446465</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5492,6 +5722,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452196</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5594,6 +5829,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452278</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5696,6 +5936,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452340</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5798,6 +6043,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452392</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5900,6 +6150,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452446</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6002,6 +6257,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452468</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6116,6 +6376,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134470975</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6218,6 +6483,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471030</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6320,6 +6590,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471064</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6422,6 +6697,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471377</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6529,6 +6809,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134519430</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6631,6 +6916,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135087727</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6742,6 +7032,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370390</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6849,6 +7144,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384823</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6955,6 +7255,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134446457</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7061,6 +7366,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452308</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7163,6 +7473,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471116</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7265,6 +7580,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471163</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7367,6 +7687,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471374</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7469,6 +7794,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471215</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7571,6 +7901,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471223</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7673,6 +8008,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471252</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7779,6 +8119,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119623430</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7889,6 +8234,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120455163</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7999,6 +8349,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120493954</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8109,6 +8464,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133997095</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8219,6 +8579,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133997219</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8316,6 +8681,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119622912</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8413,6 +8783,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119623971</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8515,6 +8890,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452234</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8617,6 +8997,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452406</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8719,6 +9104,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452426</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8826,6 +9216,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134519426</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8928,6 +9323,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370746</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9030,6 +9430,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370757</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9132,6 +9537,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134470979</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9234,6 +9644,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471102</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9336,6 +9751,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471378</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9454,8 +9874,99 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132724578</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -2325,7 +2325,7 @@
         <v>135370442</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135374857</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>135374874</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>135260102</v>
       </c>
       <c r="B29" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135087727</v>
       </c>
       <c r="B58" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>135370390</v>
       </c>
       <c r="B59" t="n">
-        <v>99094</v>
+        <v>99141</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>135384823</v>
       </c>
       <c r="B60" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>135370746</v>
       </c>
       <c r="B80" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>135370757</v>
       </c>
       <c r="B81" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -2325,7 +2325,7 @@
         <v>135370442</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>135374857</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>135374874</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>135087727</v>
       </c>
       <c r="B58" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>135370390</v>
       </c>
       <c r="B59" t="n">
-        <v>99141</v>
+        <v>99168</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>135384823</v>
       </c>
       <c r="B60" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>135370746</v>
       </c>
       <c r="B80" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>135370757</v>
       </c>
       <c r="B81" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ77"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2322,53 +2322,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132715558</v>
+        <v>135370442</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>79441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451683</v>
+        <v>451697</v>
       </c>
       <c r="R18" t="n">
-        <v>6795451</v>
+        <v>6795538</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2392,12 +2390,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2406,76 +2404,72 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132715558</t>
+          <t>https://artportalen.se/Sighting/135370442</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120461420</v>
+        <v>135374857</v>
       </c>
       <c r="B19" t="n">
-        <v>57950</v>
+        <v>79441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452004</v>
+        <v>451506</v>
       </c>
       <c r="R19" t="n">
-        <v>6795386</v>
+        <v>6795579</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,12 +2496,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,6 +2510,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2533,59 +2528,57 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120461420</t>
+          <t>https://artportalen.se/Sighting/135374857</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133881553</v>
+        <v>135374874</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>79441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451678</v>
+        <v>451511</v>
       </c>
       <c r="R20" t="n">
-        <v>6795601</v>
+        <v>6795591</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2609,27 +2602,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Levande gran</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,50 +2616,51 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133881553</t>
+          <t>https://artportalen.se/Sighting/135374874</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134471421</v>
+        <v>132715558</v>
       </c>
       <c r="B21" t="n">
-        <v>57972</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2690,27 +2669,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451503</v>
+        <v>451683</v>
       </c>
       <c r="R21" t="n">
-        <v>6795552</v>
+        <v>6795451</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2734,12 +2710,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2754,27 +2730,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471421</t>
+          <t>https://artportalen.se/Sighting/132715558</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134471435</v>
+        <v>120461420</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2799,25 +2775,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451506</v>
+        <v>452004</v>
       </c>
       <c r="R22" t="n">
-        <v>6795602</v>
+        <v>6795386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2844,12 +2820,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2875,13 +2851,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471435</t>
+          <t>https://artportalen.se/Sighting/120461420</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134519427</v>
+        <v>133881553</v>
       </c>
       <c r="B23" t="n">
         <v>57972</v>
@@ -2917,14 +2893,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451819</v>
+        <v>451678</v>
       </c>
       <c r="R23" t="n">
-        <v>6795533</v>
+        <v>6795601</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2951,22 +2927,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Levande gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2992,16 +2973,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519427</t>
+          <t>https://artportalen.se/Sighting/133881553</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120461436</v>
+        <v>134471421</v>
       </c>
       <c r="B24" t="n">
-        <v>57945</v>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,46 +2990,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451855</v>
+        <v>451503</v>
       </c>
       <c r="R24" t="n">
-        <v>6795436</v>
+        <v>6795552</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,12 +3052,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,44 +3083,48 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120461436</t>
+          <t>https://artportalen.se/Sighting/134471421</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132752338</v>
+        <v>134471435</v>
       </c>
       <c r="B25" t="n">
-        <v>57835</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100136</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3151,13 +3132,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451810</v>
+        <v>451506</v>
       </c>
       <c r="R25" t="n">
-        <v>6795373</v>
+        <v>6795602</v>
       </c>
       <c r="S25" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3181,12 +3162,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3201,27 +3182,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132752338</t>
+          <t>https://artportalen.se/Sighting/134471435</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120357924</v>
+        <v>134519427</v>
       </c>
       <c r="B26" t="n">
-        <v>57132</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,16 +3210,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3246,32 +3227,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451903</v>
+        <v>451819</v>
       </c>
       <c r="R26" t="n">
-        <v>6795337</v>
+        <v>6795533</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3295,22 +3269,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,27 +3299,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120357924</t>
+          <t>https://artportalen.se/Sighting/134519427</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120497002</v>
+        <v>120461436</v>
       </c>
       <c r="B27" t="n">
-        <v>57132</v>
+        <v>57945</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,46 +3327,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>100110</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451667</v>
+        <v>451855</v>
       </c>
       <c r="R27" t="n">
-        <v>6795441</v>
+        <v>6795436</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3419,22 +3393,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3460,66 +3424,58 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120497002</t>
+          <t>https://artportalen.se/Sighting/120461436</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121120126</v>
+        <v>132752338</v>
       </c>
       <c r="B28" t="n">
-        <v>57132</v>
+        <v>57835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>100136</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>J.R. Forster, 1772</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>451990</v>
+        <v>451810</v>
       </c>
       <c r="R28" t="n">
-        <v>6795420</v>
+        <v>6795373</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3543,12 +3499,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,27 +3519,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121120126</t>
+          <t>https://artportalen.se/Sighting/132752338</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134519429</v>
+        <v>135260102</v>
       </c>
       <c r="B29" t="n">
-        <v>57153</v>
+        <v>57167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3591,39 +3547,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451845</v>
+        <v>451568</v>
       </c>
       <c r="R29" t="n">
-        <v>6795506</v>
+        <v>6795589</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3650,22 +3606,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3691,63 +3652,66 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519429</t>
+          <t>https://artportalen.se/Sighting/135260102</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132667638</v>
+        <v>120357924</v>
       </c>
       <c r="B30" t="n">
-        <v>58410</v>
+        <v>57132</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103001</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452007</v>
+        <v>451903</v>
       </c>
       <c r="R30" t="n">
-        <v>6795396</v>
+        <v>6795337</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3771,12 +3735,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3791,27 +3765,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132667638</t>
+          <t>https://artportalen.se/Sighting/120357924</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133881550</v>
+        <v>120497002</v>
       </c>
       <c r="B31" t="n">
-        <v>58349</v>
+        <v>57132</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3819,16 +3793,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3836,22 +3810,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451505</v>
+        <v>451667</v>
       </c>
       <c r="R31" t="n">
-        <v>6795559</v>
+        <v>6795441</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,22 +3859,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3908,49 +3889,49 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133881550</t>
+          <t>https://artportalen.se/Sighting/120497002</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122780415</v>
+        <v>121120126</v>
       </c>
       <c r="B32" t="n">
-        <v>58114</v>
+        <v>57132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3960,11 +3941,7 @@
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3972,14 +3949,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451903</v>
+        <v>451990</v>
       </c>
       <c r="R32" t="n">
-        <v>6795337</v>
+        <v>6795420</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4006,22 +3983,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4047,70 +4014,59 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122780415</t>
+          <t>https://artportalen.se/Sighting/121120126</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132477046</v>
+        <v>134519429</v>
       </c>
       <c r="B33" t="n">
-        <v>58136</v>
+        <v>57153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451648</v>
+        <v>451845</v>
       </c>
       <c r="R33" t="n">
-        <v>6795608</v>
+        <v>6795506</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4134,12 +4090,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4154,27 +4120,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477046</t>
+          <t>https://artportalen.se/Sighting/134519429</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134471194</v>
+        <v>132667638</v>
       </c>
       <c r="B34" t="n">
-        <v>58136</v>
+        <v>58410</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4182,45 +4148,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451635</v>
+        <v>452007</v>
       </c>
       <c r="R34" t="n">
-        <v>6795544</v>
+        <v>6795396</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4244,12 +4211,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4264,27 +4231,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471194</t>
+          <t>https://artportalen.se/Sighting/132667638</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132477079</v>
+        <v>133881550</v>
       </c>
       <c r="B35" t="n">
-        <v>58131</v>
+        <v>58349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4292,16 +4259,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103023</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4309,32 +4276,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451648</v>
+        <v>451505</v>
       </c>
       <c r="R35" t="n">
-        <v>6795608</v>
+        <v>6795559</v>
       </c>
       <c r="S35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4358,12 +4318,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4378,27 +4348,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477079</t>
+          <t>https://artportalen.se/Sighting/133881550</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125109158</v>
+        <v>122780415</v>
       </c>
       <c r="B36" t="n">
-        <v>56522</v>
+        <v>58114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4406,49 +4376,53 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451891</v>
+        <v>451903</v>
       </c>
       <c r="R36" t="n">
-        <v>6795458</v>
+        <v>6795337</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4472,12 +4446,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4503,16 +4487,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125109158</t>
+          <t>https://artportalen.se/Sighting/122780415</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132477114</v>
+        <v>132477046</v>
       </c>
       <c r="B37" t="n">
-        <v>56539</v>
+        <v>58136</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4520,21 +4504,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4546,7 +4530,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>gående/springande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4621,46 +4605,41 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477114</t>
+          <t>https://artportalen.se/Sighting/132477046</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132918321</v>
+        <v>134471194</v>
       </c>
       <c r="B38" t="n">
-        <v>58839</v>
+        <v>58136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
@@ -4668,24 +4647,20 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451860</v>
+        <v>451635</v>
       </c>
       <c r="R38" t="n">
-        <v>6795469</v>
+        <v>6795544</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4709,12 +4684,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4723,7 +4698,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4741,16 +4715,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132918321</t>
+          <t>https://artportalen.se/Sighting/134471194</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134446393</v>
+        <v>132477079</v>
       </c>
       <c r="B39" t="n">
-        <v>99103</v>
+        <v>58131</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4758,45 +4732,49 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219788</v>
+        <v>103023</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>451856</v>
+        <v>451648</v>
       </c>
       <c r="R39" t="n">
-        <v>6795459</v>
+        <v>6795608</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4820,12 +4798,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4834,7 +4812,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4852,44 +4829,52 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446393</t>
+          <t>https://artportalen.se/Sighting/132477079</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133997108</v>
+        <v>125109158</v>
       </c>
       <c r="B40" t="n">
-        <v>99112</v>
+        <v>56522</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>206004</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4927,12 +4912,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4941,7 +4926,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4959,58 +4943,70 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997108</t>
+          <t>https://artportalen.se/Sighting/125109158</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133997151</v>
+        <v>132477114</v>
       </c>
       <c r="B41" t="n">
-        <v>99112</v>
+        <v>56539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>206004</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451900</v>
+        <v>451648</v>
       </c>
       <c r="R41" t="n">
-        <v>6795487</v>
+        <v>6795608</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5034,12 +5030,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5048,7 +5044,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5066,16 +5061,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997151</t>
+          <t>https://artportalen.se/Sighting/132477114</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134446465</v>
+        <v>132918321</v>
       </c>
       <c r="B42" t="n">
-        <v>99112</v>
+        <v>58839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5083,45 +5078,54 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451867</v>
+        <v>451860</v>
       </c>
       <c r="R42" t="n">
-        <v>6795467</v>
+        <v>6795469</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5145,12 +5149,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5177,16 +5181,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446465</t>
+          <t>https://artportalen.se/Sighting/132918321</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134452196</v>
+        <v>134446393</v>
       </c>
       <c r="B43" t="n">
-        <v>99112</v>
+        <v>99103</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5194,16 +5198,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5213,19 +5217,23 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451858</v>
+        <v>451856</v>
       </c>
       <c r="R43" t="n">
-        <v>6795529</v>
+        <v>6795459</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5284,13 +5292,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452196</t>
+          <t>https://artportalen.se/Sighting/134446393</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134452278</v>
+        <v>133997108</v>
       </c>
       <c r="B44" t="n">
         <v>99112</v>
@@ -5329,13 +5337,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451878</v>
+        <v>451891</v>
       </c>
       <c r="R44" t="n">
-        <v>6795529</v>
+        <v>6795458</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5359,12 +5367,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5391,13 +5399,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452278</t>
+          <t>https://artportalen.se/Sighting/133997108</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134452340</v>
+        <v>133997151</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5432,14 +5440,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451934</v>
+        <v>451900</v>
       </c>
       <c r="R45" t="n">
-        <v>6795489</v>
+        <v>6795487</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5466,12 +5474,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5498,13 +5506,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452340</t>
+          <t>https://artportalen.se/Sighting/133997151</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134452392</v>
+        <v>134446465</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5534,7 +5542,11 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -5543,10 +5555,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451845</v>
+        <v>451867</v>
       </c>
       <c r="R46" t="n">
-        <v>6795346</v>
+        <v>6795467</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5605,13 +5617,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452392</t>
+          <t>https://artportalen.se/Sighting/134446465</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134452446</v>
+        <v>134452196</v>
       </c>
       <c r="B47" t="n">
         <v>99112</v>
@@ -5650,10 +5662,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451876</v>
+        <v>451858</v>
       </c>
       <c r="R47" t="n">
-        <v>6795437</v>
+        <v>6795529</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5712,13 +5724,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452446</t>
+          <t>https://artportalen.se/Sighting/134452196</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134452468</v>
+        <v>134452278</v>
       </c>
       <c r="B48" t="n">
         <v>99112</v>
@@ -5757,10 +5769,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451872</v>
+        <v>451878</v>
       </c>
       <c r="R48" t="n">
-        <v>6795459</v>
+        <v>6795529</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5819,13 +5831,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452468</t>
+          <t>https://artportalen.se/Sighting/134452278</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134470975</v>
+        <v>134452340</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -5853,33 +5865,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451828</v>
+        <v>451934</v>
       </c>
       <c r="R49" t="n">
-        <v>6795362</v>
+        <v>6795489</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5906,12 +5906,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5938,13 +5938,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134470975</t>
+          <t>https://artportalen.se/Sighting/134452340</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134471030</v>
+        <v>134452392</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451822</v>
+        <v>451845</v>
       </c>
       <c r="R50" t="n">
-        <v>6795403</v>
+        <v>6795346</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6013,12 +6013,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6045,13 +6045,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471030</t>
+          <t>https://artportalen.se/Sighting/134452392</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134471064</v>
+        <v>134452446</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451754</v>
+        <v>451876</v>
       </c>
       <c r="R51" t="n">
-        <v>6795474</v>
+        <v>6795437</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6120,12 +6120,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6152,13 +6152,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471064</t>
+          <t>https://artportalen.se/Sighting/134452446</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134471377</v>
+        <v>134452468</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451524</v>
+        <v>451872</v>
       </c>
       <c r="R52" t="n">
-        <v>6795576</v>
+        <v>6795459</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6259,13 +6259,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471377</t>
+          <t>https://artportalen.se/Sighting/134452468</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134519430</v>
+        <v>134470975</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6293,20 +6293,36 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451846</v>
+        <v>451828</v>
       </c>
       <c r="R53" t="n">
-        <v>6795506</v>
+        <v>6795362</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6330,22 +6346,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6354,33 +6360,34 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519430</t>
+          <t>https://artportalen.se/Sighting/134470975</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135087727</v>
+        <v>134471030</v>
       </c>
       <c r="B54" t="n">
-        <v>99186</v>
+        <v>99112</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6412,14 +6419,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451853</v>
+        <v>451822</v>
       </c>
       <c r="R54" t="n">
-        <v>6795315</v>
+        <v>6795403</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6446,12 +6453,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6478,16 +6485,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135087727</t>
+          <t>https://artportalen.se/Sighting/134471030</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134446457</v>
+        <v>134471064</v>
       </c>
       <c r="B55" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6495,30 +6502,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
@@ -6527,10 +6530,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451867</v>
+        <v>451754</v>
       </c>
       <c r="R55" t="n">
-        <v>6795467</v>
+        <v>6795474</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6557,12 +6560,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6589,16 +6592,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446457</t>
+          <t>https://artportalen.se/Sighting/134471064</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134452308</v>
+        <v>134471377</v>
       </c>
       <c r="B56" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6606,30 +6609,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
@@ -6638,10 +6637,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451924</v>
+        <v>451524</v>
       </c>
       <c r="R56" t="n">
-        <v>6795490</v>
+        <v>6795576</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6668,12 +6667,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6700,16 +6699,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452308</t>
+          <t>https://artportalen.se/Sighting/134471377</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134471116</v>
+        <v>134519430</v>
       </c>
       <c r="B57" t="n">
-        <v>99099</v>
+        <v>99112</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6717,41 +6716,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451657</v>
+        <v>451846</v>
       </c>
       <c r="R57" t="n">
-        <v>6795504</v>
+        <v>6795506</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6775,12 +6770,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6789,34 +6794,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471116</t>
+          <t>https://artportalen.se/Sighting/134519430</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134471163</v>
+        <v>135087727</v>
       </c>
       <c r="B58" t="n">
-        <v>99099</v>
+        <v>99186</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6824,21 +6828,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6848,14 +6852,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451656</v>
+        <v>451853</v>
       </c>
       <c r="R58" t="n">
-        <v>6795514</v>
+        <v>6795315</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6882,12 +6886,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6914,16 +6918,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471163</t>
+          <t>https://artportalen.se/Sighting/135087727</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134471374</v>
+        <v>135370390</v>
       </c>
       <c r="B59" t="n">
-        <v>99099</v>
+        <v>99173</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6931,38 +6935,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220093</v>
+        <v>219795</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451524</v>
+        <v>451924</v>
       </c>
       <c r="R59" t="n">
-        <v>6795576</v>
+        <v>6795456</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6989,12 +6997,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>I källmiljö</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7021,16 +7034,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471374</t>
+          <t>https://artportalen.se/Sighting/135370390</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134471215</v>
+        <v>135896094</v>
       </c>
       <c r="B60" t="n">
-        <v>108274</v>
+        <v>99173</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7038,21 +7051,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220102</v>
+        <v>219795</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7062,14 +7075,14 @@
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451641</v>
+        <v>451940</v>
       </c>
       <c r="R60" t="n">
-        <v>6795575</v>
+        <v>6795495</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7096,12 +7109,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7128,16 +7141,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471215</t>
+          <t>https://artportalen.se/Sighting/135896094</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134471223</v>
+        <v>135384823</v>
       </c>
       <c r="B61" t="n">
-        <v>108274</v>
+        <v>108292</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7145,21 +7158,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7203,12 +7216,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Invid källbäck</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7235,16 +7253,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471223</t>
+          <t>https://artportalen.se/Sighting/135384823</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134471252</v>
+        <v>134446457</v>
       </c>
       <c r="B62" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7252,26 +7270,30 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
@@ -7280,10 +7302,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>451628</v>
+        <v>451867</v>
       </c>
       <c r="R62" t="n">
-        <v>6795600</v>
+        <v>6795467</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7310,12 +7332,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7342,60 +7364,59 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471252</t>
+          <t>https://artportalen.se/Sighting/134446457</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119623430</v>
+        <v>134452308</v>
       </c>
       <c r="B63" t="n">
-        <v>99118</v>
+        <v>99099</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452010</v>
+        <v>451924</v>
       </c>
       <c r="R63" t="n">
-        <v>6795395</v>
+        <v>6795490</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7422,12 +7443,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7436,80 +7457,73 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623430</t>
+          <t>https://artportalen.se/Sighting/134452308</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120455163</v>
+        <v>134471116</v>
       </c>
       <c r="B64" t="n">
-        <v>99118</v>
+        <v>99099</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452004</v>
+        <v>451657</v>
       </c>
       <c r="R64" t="n">
-        <v>6795386</v>
+        <v>6795504</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7536,12 +7550,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7568,63 +7582,55 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120455163</t>
+          <t>https://artportalen.se/Sighting/134471116</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120493954</v>
+        <v>134471163</v>
       </c>
       <c r="B65" t="n">
-        <v>99118</v>
+        <v>99099</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451990</v>
+        <v>451656</v>
       </c>
       <c r="R65" t="n">
-        <v>6795420</v>
+        <v>6795514</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7651,12 +7657,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7683,63 +7689,55 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493954</t>
+          <t>https://artportalen.se/Sighting/134471163</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133997095</v>
+        <v>134471374</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>99099</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>451903</v>
+        <v>451524</v>
       </c>
       <c r="R66" t="n">
-        <v>6795472</v>
+        <v>6795576</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7766,12 +7764,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7798,50 +7796,42 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997095</t>
+          <t>https://artportalen.se/Sighting/134471374</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133997219</v>
+        <v>134471215</v>
       </c>
       <c r="B67" t="n">
-        <v>99195</v>
+        <v>108274</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -7851,10 +7841,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451888</v>
+        <v>451641</v>
       </c>
       <c r="R67" t="n">
-        <v>6795475</v>
+        <v>6795575</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7881,12 +7871,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7913,16 +7903,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997219</t>
+          <t>https://artportalen.se/Sighting/134471215</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119622912</v>
+        <v>134471223</v>
       </c>
       <c r="B68" t="n">
-        <v>106229</v>
+        <v>108274</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7930,34 +7920,38 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221725</v>
+        <v>220102</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452035</v>
+        <v>451640</v>
       </c>
       <c r="R68" t="n">
-        <v>6795377</v>
+        <v>6795589</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7984,12 +7978,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7998,33 +7992,34 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119622912</t>
+          <t>https://artportalen.se/Sighting/134471223</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119623971</v>
+        <v>134471252</v>
       </c>
       <c r="B69" t="n">
-        <v>106229</v>
+        <v>108274</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8032,34 +8027,38 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221725</v>
+        <v>220102</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>451957</v>
+        <v>451628</v>
       </c>
       <c r="R69" t="n">
-        <v>6795424</v>
+        <v>6795600</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8086,12 +8085,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8100,72 +8099,78 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623971</t>
+          <t>https://artportalen.se/Sighting/134471252</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134452234</v>
+        <v>119623430</v>
       </c>
       <c r="B70" t="n">
-        <v>98060</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>451878</v>
+        <v>452010</v>
       </c>
       <c r="R70" t="n">
-        <v>6795529</v>
+        <v>6795395</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8192,12 +8197,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8206,73 +8211,80 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452234</t>
+          <t>https://artportalen.se/Sighting/119623430</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134452406</v>
+        <v>120455163</v>
       </c>
       <c r="B71" t="n">
-        <v>98060</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>451858</v>
+        <v>452004</v>
       </c>
       <c r="R71" t="n">
-        <v>6795410</v>
+        <v>6795386</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8299,12 +8311,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8331,55 +8343,63 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452406</t>
+          <t>https://artportalen.se/Sighting/120455163</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134452426</v>
+        <v>120493954</v>
       </c>
       <c r="B72" t="n">
-        <v>98060</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>451875</v>
+        <v>451990</v>
       </c>
       <c r="R72" t="n">
-        <v>6795422</v>
+        <v>6795420</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8406,12 +8426,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8438,54 +8458,66 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452426</t>
+          <t>https://artportalen.se/Sighting/120493954</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134519426</v>
+        <v>133997095</v>
       </c>
       <c r="B73" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>451669</v>
+        <v>451903</v>
       </c>
       <c r="R73" t="n">
-        <v>6795570</v>
+        <v>6795472</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8509,22 +8541,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8533,59 +8555,68 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519426</t>
+          <t>https://artportalen.se/Sighting/133997095</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134470979</v>
+        <v>133997219</v>
       </c>
       <c r="B74" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -8595,10 +8626,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>451828</v>
+        <v>451888</v>
       </c>
       <c r="R74" t="n">
-        <v>6795362</v>
+        <v>6795475</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8625,12 +8656,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8657,16 +8688,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134470979</t>
+          <t>https://artportalen.se/Sighting/133997219</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134471102</v>
+        <v>119622912</v>
       </c>
       <c r="B75" t="n">
-        <v>99217</v>
+        <v>106229</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,38 +8705,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>451693</v>
+        <v>452035</v>
       </c>
       <c r="R75" t="n">
-        <v>6795486</v>
+        <v>6795377</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8732,12 +8759,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8746,34 +8773,33 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471102</t>
+          <t>https://artportalen.se/Sighting/119622912</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134471378</v>
+        <v>119623971</v>
       </c>
       <c r="B76" t="n">
-        <v>99217</v>
+        <v>106229</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8781,38 +8807,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>451524</v>
+        <v>451957</v>
       </c>
       <c r="R76" t="n">
-        <v>6795576</v>
+        <v>6795424</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8839,12 +8861,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8853,34 +8875,33 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471378</t>
+          <t>https://artportalen.se/Sighting/119623971</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132724578</v>
+        <v>135896078</v>
       </c>
       <c r="B77" t="n">
-        <v>101403</v>
+        <v>106396</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8888,57 +8909,41 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>451910</v>
+        <v>452073</v>
       </c>
       <c r="R77" t="n">
-        <v>6795497</v>
+        <v>6795385</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8962,12 +8967,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8993,6 +8998,1097 @@
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135896078</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>134452234</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>451878</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6795529</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452234</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>134452406</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>451858</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6795410</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452406</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134452426</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>451875</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6795422</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134452426</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134519426</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Käsdajk-Övergärd, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>451669</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6795570</v>
+      </c>
+      <c r="S81" t="n">
+        <v>8</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jenni Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134519426</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135370746</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>451924</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6795456</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370746</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135370757</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>451910</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6795497</v>
+      </c>
+      <c r="S83" t="n">
+        <v>25</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135370757</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134470979</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>451828</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6795362</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134470979</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134471102</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>451693</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6795486</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471102</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134471378</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>451524</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6795576</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471378</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>132724578</v>
+      </c>
+      <c r="B87" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>451910</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6795497</v>
+      </c>
+      <c r="S87" t="n">
+        <v>25</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132724578</t>
         </is>
@@ -9076,6 +10172,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -6927,7 +6927,7 @@
         <v>135370390</v>
       </c>
       <c r="B59" t="n">
-        <v>99173</v>
+        <v>99175</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>135896094</v>
       </c>
       <c r="B60" t="n">
-        <v>99173</v>
+        <v>99175</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>135384823</v>
       </c>
       <c r="B61" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>135896078</v>
       </c>
       <c r="B77" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>135370746</v>
       </c>
       <c r="B82" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>135370757</v>
       </c>
       <c r="B83" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ87"/>
+  <dimension ref="A1:AZ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4721,60 +4721,52 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132477079</v>
+        <v>135940024</v>
       </c>
       <c r="B39" t="n">
-        <v>58131</v>
+        <v>58141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>451648</v>
+        <v>451757</v>
       </c>
       <c r="R39" t="n">
-        <v>6795608</v>
+        <v>6795445</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4798,12 +4790,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4829,66 +4821,66 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477079</t>
+          <t>https://artportalen.se/Sighting/135940024</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125109158</v>
+        <v>132477079</v>
       </c>
       <c r="B40" t="n">
-        <v>56522</v>
+        <v>58131</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>206004</v>
+        <v>103023</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451891</v>
+        <v>451648</v>
       </c>
       <c r="R40" t="n">
-        <v>6795458</v>
+        <v>6795608</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4912,12 +4904,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4943,16 +4935,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125109158</t>
+          <t>https://artportalen.se/Sighting/132477079</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132477114</v>
+        <v>125109158</v>
       </c>
       <c r="B41" t="n">
-        <v>56539</v>
+        <v>56522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4989,24 +4981,20 @@
           <t>gående/springande</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451648</v>
+        <v>451891</v>
       </c>
       <c r="R41" t="n">
-        <v>6795608</v>
+        <v>6795458</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5030,12 +5018,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5061,33 +5049,33 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477114</t>
+          <t>https://artportalen.se/Sighting/125109158</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132918321</v>
+        <v>132477114</v>
       </c>
       <c r="B42" t="n">
-        <v>58839</v>
+        <v>56539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5097,15 +5085,14 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5119,13 +5106,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451860</v>
+        <v>451648</v>
       </c>
       <c r="R42" t="n">
-        <v>6795469</v>
+        <v>6795608</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5149,12 +5136,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5163,7 +5150,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5181,16 +5167,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132918321</t>
+          <t>https://artportalen.se/Sighting/132477114</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134446393</v>
+        <v>132918321</v>
       </c>
       <c r="B43" t="n">
-        <v>99103</v>
+        <v>58839</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5198,45 +5184,54 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219788</v>
+        <v>208249</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451856</v>
+        <v>451860</v>
       </c>
       <c r="R43" t="n">
-        <v>6795459</v>
+        <v>6795469</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5260,12 +5255,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5292,16 +5287,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446393</t>
+          <t>https://artportalen.se/Sighting/132918321</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133997108</v>
+        <v>134446393</v>
       </c>
       <c r="B44" t="n">
-        <v>99112</v>
+        <v>99103</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,16 +5304,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5328,22 +5323,26 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451891</v>
+        <v>451856</v>
       </c>
       <c r="R44" t="n">
-        <v>6795458</v>
+        <v>6795459</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5367,12 +5366,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5399,13 +5398,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997108</t>
+          <t>https://artportalen.se/Sighting/134446393</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133997151</v>
+        <v>133997108</v>
       </c>
       <c r="B45" t="n">
         <v>99112</v>
@@ -5440,17 +5439,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451900</v>
+        <v>451891</v>
       </c>
       <c r="R45" t="n">
-        <v>6795487</v>
+        <v>6795458</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5506,13 +5505,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997151</t>
+          <t>https://artportalen.se/Sighting/133997108</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134446465</v>
+        <v>133997151</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5542,23 +5541,19 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451867</v>
+        <v>451900</v>
       </c>
       <c r="R46" t="n">
-        <v>6795467</v>
+        <v>6795487</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5585,12 +5580,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5617,13 +5612,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446465</t>
+          <t>https://artportalen.se/Sighting/133997151</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134452196</v>
+        <v>134446465</v>
       </c>
       <c r="B47" t="n">
         <v>99112</v>
@@ -5653,7 +5648,11 @@
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
@@ -5662,10 +5661,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451858</v>
+        <v>451867</v>
       </c>
       <c r="R47" t="n">
-        <v>6795529</v>
+        <v>6795467</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5724,13 +5723,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452196</t>
+          <t>https://artportalen.se/Sighting/134446465</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134452278</v>
+        <v>134452196</v>
       </c>
       <c r="B48" t="n">
         <v>99112</v>
@@ -5769,7 +5768,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451878</v>
+        <v>451858</v>
       </c>
       <c r="R48" t="n">
         <v>6795529</v>
@@ -5831,13 +5830,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452278</t>
+          <t>https://artportalen.se/Sighting/134452196</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134452340</v>
+        <v>134452278</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -5876,10 +5875,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451934</v>
+        <v>451878</v>
       </c>
       <c r="R49" t="n">
-        <v>6795489</v>
+        <v>6795529</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5938,13 +5937,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452340</t>
+          <t>https://artportalen.se/Sighting/134452278</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134452392</v>
+        <v>134452340</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -5983,10 +5982,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451845</v>
+        <v>451934</v>
       </c>
       <c r="R50" t="n">
-        <v>6795346</v>
+        <v>6795489</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6045,13 +6044,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452392</t>
+          <t>https://artportalen.se/Sighting/134452340</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134452446</v>
+        <v>134452392</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -6090,10 +6089,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451876</v>
+        <v>451845</v>
       </c>
       <c r="R51" t="n">
-        <v>6795437</v>
+        <v>6795346</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6152,13 +6151,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452446</t>
+          <t>https://artportalen.se/Sighting/134452392</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134452468</v>
+        <v>134452446</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -6197,10 +6196,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451872</v>
+        <v>451876</v>
       </c>
       <c r="R52" t="n">
-        <v>6795459</v>
+        <v>6795437</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6259,13 +6258,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452468</t>
+          <t>https://artportalen.se/Sighting/134452446</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134470975</v>
+        <v>134452468</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6293,33 +6292,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451828</v>
+        <v>451872</v>
       </c>
       <c r="R53" t="n">
-        <v>6795362</v>
+        <v>6795459</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6346,12 +6333,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6378,13 +6365,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134470975</t>
+          <t>https://artportalen.se/Sighting/134452468</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134471030</v>
+        <v>134470975</v>
       </c>
       <c r="B54" t="n">
         <v>99112</v>
@@ -6412,21 +6399,33 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451822</v>
+        <v>451828</v>
       </c>
       <c r="R54" t="n">
-        <v>6795403</v>
+        <v>6795362</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6485,13 +6484,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471030</t>
+          <t>https://artportalen.se/Sighting/134470975</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134471064</v>
+        <v>134471030</v>
       </c>
       <c r="B55" t="n">
         <v>99112</v>
@@ -6530,10 +6529,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451754</v>
+        <v>451822</v>
       </c>
       <c r="R55" t="n">
-        <v>6795474</v>
+        <v>6795403</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6592,13 +6591,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471064</t>
+          <t>https://artportalen.se/Sighting/134471030</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134471377</v>
+        <v>134471064</v>
       </c>
       <c r="B56" t="n">
         <v>99112</v>
@@ -6637,10 +6636,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451524</v>
+        <v>451754</v>
       </c>
       <c r="R56" t="n">
-        <v>6795576</v>
+        <v>6795474</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6699,13 +6698,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471377</t>
+          <t>https://artportalen.se/Sighting/134471064</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134519430</v>
+        <v>134471377</v>
       </c>
       <c r="B57" t="n">
         <v>99112</v>
@@ -6734,19 +6733,23 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451846</v>
+        <v>451524</v>
       </c>
       <c r="R57" t="n">
-        <v>6795506</v>
+        <v>6795576</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6770,22 +6773,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6794,33 +6787,34 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519430</t>
+          <t>https://artportalen.se/Sighting/134471377</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135087727</v>
+        <v>134519430</v>
       </c>
       <c r="B58" t="n">
-        <v>99186</v>
+        <v>99112</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6846,23 +6840,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451853</v>
+        <v>451846</v>
       </c>
       <c r="R58" t="n">
-        <v>6795315</v>
+        <v>6795506</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6886,12 +6876,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6900,34 +6900,33 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135087727</t>
+          <t>https://artportalen.se/Sighting/134519430</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135370390</v>
+        <v>135087727</v>
       </c>
       <c r="B59" t="n">
-        <v>99175</v>
+        <v>99186</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6935,42 +6934,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451924</v>
+        <v>451853</v>
       </c>
       <c r="R59" t="n">
-        <v>6795456</v>
+        <v>6795315</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6997,17 +6992,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>I källmiljö</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7034,16 +7024,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370390</t>
+          <t>https://artportalen.se/Sighting/135087727</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135896094</v>
+        <v>135940067</v>
       </c>
       <c r="B60" t="n">
-        <v>99175</v>
+        <v>99193</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7051,38 +7041,46 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451940</v>
+        <v>451650</v>
       </c>
       <c r="R60" t="n">
-        <v>6795495</v>
+        <v>6795625</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7109,12 +7107,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7141,16 +7139,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135896094</t>
+          <t>https://artportalen.se/Sighting/135940067</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135384823</v>
+        <v>135370390</v>
       </c>
       <c r="B61" t="n">
-        <v>108294</v>
+        <v>99175</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7158,38 +7156,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220083</v>
+        <v>219795</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451640</v>
+        <v>451924</v>
       </c>
       <c r="R61" t="n">
-        <v>6795589</v>
+        <v>6795456</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7226,7 +7228,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Invid källbäck</t>
+          <t>I källmiljö</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7253,16 +7255,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384823</t>
+          <t>https://artportalen.se/Sighting/135370390</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134446457</v>
+        <v>135896094</v>
       </c>
       <c r="B62" t="n">
-        <v>99099</v>
+        <v>99175</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7270,42 +7272,38 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220093</v>
+        <v>219795</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>451867</v>
+        <v>451940</v>
       </c>
       <c r="R62" t="n">
-        <v>6795467</v>
+        <v>6795495</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7332,12 +7330,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7364,16 +7362,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446457</t>
+          <t>https://artportalen.se/Sighting/135896094</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134452308</v>
+        <v>135384823</v>
       </c>
       <c r="B63" t="n">
-        <v>99099</v>
+        <v>108294</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7381,30 +7379,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220093</v>
+        <v>220083</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -7413,10 +7407,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>451924</v>
+        <v>451640</v>
       </c>
       <c r="R63" t="n">
-        <v>6795490</v>
+        <v>6795589</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7443,12 +7437,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Invid källbäck</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7475,13 +7474,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452308</t>
+          <t>https://artportalen.se/Sighting/135384823</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134471116</v>
+        <v>134446457</v>
       </c>
       <c r="B64" t="n">
         <v>99099</v>
@@ -7511,7 +7510,11 @@
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -7520,10 +7523,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>451657</v>
+        <v>451867</v>
       </c>
       <c r="R64" t="n">
-        <v>6795504</v>
+        <v>6795467</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7550,12 +7553,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7582,13 +7585,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471116</t>
+          <t>https://artportalen.se/Sighting/134446457</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134471163</v>
+        <v>134452308</v>
       </c>
       <c r="B65" t="n">
         <v>99099</v>
@@ -7618,7 +7621,11 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -7627,10 +7634,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451656</v>
+        <v>451924</v>
       </c>
       <c r="R65" t="n">
-        <v>6795514</v>
+        <v>6795490</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7657,12 +7664,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7689,13 +7696,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471163</t>
+          <t>https://artportalen.se/Sighting/134452308</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134471374</v>
+        <v>134471116</v>
       </c>
       <c r="B66" t="n">
         <v>99099</v>
@@ -7734,10 +7741,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>451524</v>
+        <v>451657</v>
       </c>
       <c r="R66" t="n">
-        <v>6795576</v>
+        <v>6795504</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7796,16 +7803,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471374</t>
+          <t>https://artportalen.se/Sighting/134471116</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134471215</v>
+        <v>134471163</v>
       </c>
       <c r="B67" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7813,21 +7820,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7837,14 +7844,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451641</v>
+        <v>451656</v>
       </c>
       <c r="R67" t="n">
-        <v>6795575</v>
+        <v>6795514</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7903,16 +7910,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471215</t>
+          <t>https://artportalen.se/Sighting/134471163</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134471223</v>
+        <v>134471374</v>
       </c>
       <c r="B68" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7920,21 +7927,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7948,10 +7955,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>451640</v>
+        <v>451524</v>
       </c>
       <c r="R68" t="n">
-        <v>6795589</v>
+        <v>6795576</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8010,13 +8017,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471223</t>
+          <t>https://artportalen.se/Sighting/134471374</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134471252</v>
+        <v>134471215</v>
       </c>
       <c r="B69" t="n">
         <v>108274</v>
@@ -8051,14 +8058,14 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>451628</v>
+        <v>451641</v>
       </c>
       <c r="R69" t="n">
-        <v>6795600</v>
+        <v>6795575</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8117,60 +8124,55 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471252</t>
+          <t>https://artportalen.se/Sighting/134471215</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119623430</v>
+        <v>134471223</v>
       </c>
       <c r="B70" t="n">
-        <v>99118</v>
+        <v>108274</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452010</v>
+        <v>451640</v>
       </c>
       <c r="R70" t="n">
-        <v>6795395</v>
+        <v>6795589</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8197,12 +8199,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8211,80 +8213,73 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623430</t>
+          <t>https://artportalen.se/Sighting/134471223</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120455163</v>
+        <v>134471252</v>
       </c>
       <c r="B71" t="n">
-        <v>99118</v>
+        <v>108274</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452004</v>
+        <v>451628</v>
       </c>
       <c r="R71" t="n">
-        <v>6795386</v>
+        <v>6795600</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8311,12 +8306,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8343,13 +8338,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120455163</t>
+          <t>https://artportalen.se/Sighting/134471252</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120493954</v>
+        <v>119623430</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8379,7 +8374,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8387,19 +8382,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>451990</v>
+        <v>452010</v>
       </c>
       <c r="R72" t="n">
-        <v>6795420</v>
+        <v>6795395</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8426,12 +8418,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8440,34 +8432,33 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493954</t>
+          <t>https://artportalen.se/Sighting/119623430</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133997095</v>
+        <v>120455163</v>
       </c>
       <c r="B73" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8494,12 +8485,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -8507,14 +8498,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>451903</v>
+        <v>452004</v>
       </c>
       <c r="R73" t="n">
-        <v>6795472</v>
+        <v>6795386</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8541,12 +8532,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8573,16 +8564,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997095</t>
+          <t>https://artportalen.se/Sighting/120455163</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133997219</v>
+        <v>120493954</v>
       </c>
       <c r="B74" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8609,12 +8600,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -8622,14 +8613,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>451888</v>
+        <v>451990</v>
       </c>
       <c r="R74" t="n">
-        <v>6795475</v>
+        <v>6795420</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8656,12 +8647,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8688,51 +8679,63 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997219</t>
+          <t>https://artportalen.se/Sighting/120493954</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119622912</v>
+        <v>133997095</v>
       </c>
       <c r="B75" t="n">
-        <v>106229</v>
+        <v>99195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452035</v>
+        <v>451903</v>
       </c>
       <c r="R75" t="n">
-        <v>6795377</v>
+        <v>6795472</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8759,12 +8762,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8773,68 +8776,81 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119622912</t>
+          <t>https://artportalen.se/Sighting/133997095</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119623971</v>
+        <v>133997219</v>
       </c>
       <c r="B76" t="n">
-        <v>106229</v>
+        <v>99195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>451957</v>
+        <v>451888</v>
       </c>
       <c r="R76" t="n">
-        <v>6795424</v>
+        <v>6795475</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8861,12 +8877,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8875,33 +8891,34 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623971</t>
+          <t>https://artportalen.se/Sighting/133997219</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135896078</v>
+        <v>119622912</v>
       </c>
       <c r="B77" t="n">
-        <v>106398</v>
+        <v>106229</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8927,20 +8944,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452073</v>
+        <v>452035</v>
       </c>
       <c r="R77" t="n">
-        <v>6795385</v>
+        <v>6795377</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8967,12 +8980,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8981,34 +8994,33 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135896078</t>
+          <t>https://artportalen.se/Sighting/119622912</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134452234</v>
+        <v>119623971</v>
       </c>
       <c r="B78" t="n">
-        <v>98060</v>
+        <v>106229</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9016,38 +9028,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>451878</v>
+        <v>451957</v>
       </c>
       <c r="R78" t="n">
-        <v>6795529</v>
+        <v>6795424</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9074,12 +9082,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9088,34 +9096,33 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452234</t>
+          <t>https://artportalen.se/Sighting/119623971</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134452406</v>
+        <v>135896078</v>
       </c>
       <c r="B79" t="n">
-        <v>98060</v>
+        <v>106398</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9123,21 +9130,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9147,14 +9154,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>451858</v>
+        <v>452073</v>
       </c>
       <c r="R79" t="n">
-        <v>6795410</v>
+        <v>6795385</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9181,12 +9188,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9213,13 +9220,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452406</t>
+          <t>https://artportalen.se/Sighting/135896078</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134452426</v>
+        <v>134452234</v>
       </c>
       <c r="B80" t="n">
         <v>98060</v>
@@ -9258,10 +9265,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>451875</v>
+        <v>451878</v>
       </c>
       <c r="R80" t="n">
-        <v>6795422</v>
+        <v>6795529</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9320,13 +9327,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452426</t>
+          <t>https://artportalen.se/Sighting/134452234</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134519426</v>
+        <v>134452406</v>
       </c>
       <c r="B81" t="n">
         <v>98060</v>
@@ -9355,19 +9362,23 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>451669</v>
+        <v>451858</v>
       </c>
       <c r="R81" t="n">
-        <v>6795570</v>
+        <v>6795410</v>
       </c>
       <c r="S81" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9391,22 +9402,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9415,33 +9416,34 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519426</t>
+          <t>https://artportalen.se/Sighting/134452406</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135370746</v>
+        <v>134452426</v>
       </c>
       <c r="B82" t="n">
-        <v>98138</v>
+        <v>98060</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9473,14 +9475,14 @@
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>451924</v>
+        <v>451875</v>
       </c>
       <c r="R82" t="n">
-        <v>6795456</v>
+        <v>6795422</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9507,12 +9509,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9539,16 +9541,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370746</t>
+          <t>https://artportalen.se/Sighting/134452426</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135370757</v>
+        <v>134519426</v>
       </c>
       <c r="B83" t="n">
-        <v>98138</v>
+        <v>98060</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9574,23 +9576,19 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>451910</v>
+        <v>451669</v>
       </c>
       <c r="R83" t="n">
-        <v>6795497</v>
+        <v>6795570</v>
       </c>
       <c r="S83" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9614,12 +9612,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9628,34 +9636,33 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370757</t>
+          <t>https://artportalen.se/Sighting/134519426</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134470979</v>
+        <v>135370746</v>
       </c>
       <c r="B84" t="n">
-        <v>99217</v>
+        <v>98138</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,21 +9670,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9691,10 +9698,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>451828</v>
+        <v>451924</v>
       </c>
       <c r="R84" t="n">
-        <v>6795362</v>
+        <v>6795456</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9721,12 +9728,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9753,16 +9760,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134470979</t>
+          <t>https://artportalen.se/Sighting/135370746</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134471102</v>
+        <v>135370757</v>
       </c>
       <c r="B85" t="n">
-        <v>99217</v>
+        <v>98138</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9770,21 +9777,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9798,13 +9805,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>451693</v>
+        <v>451910</v>
       </c>
       <c r="R85" t="n">
-        <v>6795486</v>
+        <v>6795497</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9828,12 +9835,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9860,13 +9867,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471102</t>
+          <t>https://artportalen.se/Sighting/135370757</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134471378</v>
+        <v>134470979</v>
       </c>
       <c r="B86" t="n">
         <v>99217</v>
@@ -9901,14 +9908,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451524</v>
+        <v>451828</v>
       </c>
       <c r="R86" t="n">
-        <v>6795576</v>
+        <v>6795362</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9967,16 +9974,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471378</t>
+          <t>https://artportalen.se/Sighting/134470979</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132724578</v>
+        <v>134471102</v>
       </c>
       <c r="B87" t="n">
-        <v>101403</v>
+        <v>99217</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9984,57 +9991,41 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>451910</v>
+        <v>451693</v>
       </c>
       <c r="R87" t="n">
-        <v>6795497</v>
+        <v>6795486</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10058,12 +10049,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10089,6 +10080,236 @@
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471102</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>134471378</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>451524</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6795576</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471378</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>132724578</v>
+      </c>
+      <c r="B89" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>451910</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6795497</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132724578</t>
         </is>
@@ -10182,6 +10403,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4724,7 +4724,7 @@
         <v>135940024</v>
       </c>
       <c r="B39" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         <v>135940067</v>
       </c>
       <c r="B60" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>135896094</v>
       </c>
       <c r="B62" t="n">
-        <v>99175</v>
+        <v>99192</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>135896078</v>
       </c>
       <c r="B79" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -7033,7 +7033,7 @@
         <v>135940067</v>
       </c>
       <c r="B60" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>135896094</v>
       </c>
       <c r="B62" t="n">
-        <v>99192</v>
+        <v>99193</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>135896078</v>
       </c>
       <c r="B79" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ89"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4137,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132667638</v>
+        <v>136240267</v>
       </c>
       <c r="B34" t="n">
-        <v>58410</v>
+        <v>57823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4148,46 +4148,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103001</v>
+        <v>102621</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Övergärd, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452007</v>
+        <v>452004</v>
       </c>
       <c r="R34" t="n">
-        <v>6795396</v>
+        <v>6795386</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4211,12 +4210,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4231,52 +4230,56 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132667638</t>
+          <t>https://artportalen.se/Sighting/136240267</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133881550</v>
+        <v>132667638</v>
       </c>
       <c r="B35" t="n">
-        <v>58349</v>
+        <v>58410</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -4284,17 +4287,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>451505</v>
+        <v>452007</v>
       </c>
       <c r="R35" t="n">
-        <v>6795559</v>
+        <v>6795396</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4318,22 +4321,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4359,67 +4352,56 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133881550</t>
+          <t>https://artportalen.se/Sighting/132667638</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122780415</v>
+        <v>133881550</v>
       </c>
       <c r="B36" t="n">
-        <v>58114</v>
+        <v>58349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451903</v>
+        <v>451505</v>
       </c>
       <c r="R36" t="n">
-        <v>6795337</v>
+        <v>6795559</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4446,22 +4428,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4476,27 +4458,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122780415</t>
+          <t>https://artportalen.se/Sighting/133881550</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132477046</v>
+        <v>122780415</v>
       </c>
       <c r="B37" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4523,14 +4505,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4544,13 +4526,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451648</v>
+        <v>451903</v>
       </c>
       <c r="R37" t="n">
-        <v>6795608</v>
+        <v>6795337</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4574,12 +4556,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4605,13 +4597,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477046</t>
+          <t>https://artportalen.se/Sighting/122780415</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134471194</v>
+        <v>132477046</v>
       </c>
       <c r="B38" t="n">
         <v>58136</v>
@@ -4639,7 +4631,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
@@ -4647,20 +4643,24 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451635</v>
+        <v>451648</v>
       </c>
       <c r="R38" t="n">
-        <v>6795544</v>
+        <v>6795608</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4684,12 +4684,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4715,16 +4715,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471194</t>
+          <t>https://artportalen.se/Sighting/132477046</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135940024</v>
+        <v>134471194</v>
       </c>
       <c r="B39" t="n">
-        <v>58143</v>
+        <v>58136</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,11 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4760,10 +4764,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>451757</v>
+        <v>451635</v>
       </c>
       <c r="R39" t="n">
-        <v>6795445</v>
+        <v>6795544</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4790,12 +4794,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4821,66 +4825,58 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135940024</t>
+          <t>https://artportalen.se/Sighting/134471194</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132477079</v>
+        <v>135940024</v>
       </c>
       <c r="B40" t="n">
-        <v>58131</v>
+        <v>58143</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451648</v>
+        <v>451757</v>
       </c>
       <c r="R40" t="n">
-        <v>6795608</v>
+        <v>6795445</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4904,12 +4900,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4935,66 +4931,66 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477079</t>
+          <t>https://artportalen.se/Sighting/135940024</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125109158</v>
+        <v>132477079</v>
       </c>
       <c r="B41" t="n">
-        <v>56522</v>
+        <v>58131</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>206004</v>
+        <v>103023</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451891</v>
+        <v>451648</v>
       </c>
       <c r="R41" t="n">
-        <v>6795458</v>
+        <v>6795608</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5018,12 +5014,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5049,16 +5045,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125109158</t>
+          <t>https://artportalen.se/Sighting/132477079</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132477114</v>
+        <v>125109158</v>
       </c>
       <c r="B42" t="n">
-        <v>56539</v>
+        <v>56522</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5095,24 +5091,20 @@
           <t>gående/springande</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451648</v>
+        <v>451891</v>
       </c>
       <c r="R42" t="n">
-        <v>6795608</v>
+        <v>6795458</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5136,12 +5128,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5167,33 +5159,33 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477114</t>
+          <t>https://artportalen.se/Sighting/125109158</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132918321</v>
+        <v>132477114</v>
       </c>
       <c r="B43" t="n">
-        <v>58839</v>
+        <v>56539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5203,15 +5195,14 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5225,13 +5216,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451860</v>
+        <v>451648</v>
       </c>
       <c r="R43" t="n">
-        <v>6795469</v>
+        <v>6795608</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5255,12 +5246,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5269,7 +5260,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5287,16 +5277,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132918321</t>
+          <t>https://artportalen.se/Sighting/132477114</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134446393</v>
+        <v>132918321</v>
       </c>
       <c r="B44" t="n">
-        <v>99103</v>
+        <v>58839</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5304,45 +5294,54 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219788</v>
+        <v>208249</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451856</v>
+        <v>451860</v>
       </c>
       <c r="R44" t="n">
-        <v>6795459</v>
+        <v>6795469</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5366,12 +5365,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5398,16 +5397,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446393</t>
+          <t>https://artportalen.se/Sighting/132918321</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133997108</v>
+        <v>134446393</v>
       </c>
       <c r="B45" t="n">
-        <v>99112</v>
+        <v>99103</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5415,16 +5414,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5434,22 +5433,26 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451891</v>
+        <v>451856</v>
       </c>
       <c r="R45" t="n">
-        <v>6795458</v>
+        <v>6795459</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5473,12 +5476,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5505,13 +5508,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997108</t>
+          <t>https://artportalen.se/Sighting/134446393</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133997151</v>
+        <v>133997108</v>
       </c>
       <c r="B46" t="n">
         <v>99112</v>
@@ -5546,17 +5549,17 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451900</v>
+        <v>451891</v>
       </c>
       <c r="R46" t="n">
-        <v>6795487</v>
+        <v>6795458</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5612,13 +5615,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997151</t>
+          <t>https://artportalen.se/Sighting/133997108</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134446465</v>
+        <v>133997151</v>
       </c>
       <c r="B47" t="n">
         <v>99112</v>
@@ -5648,23 +5651,19 @@
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451867</v>
+        <v>451900</v>
       </c>
       <c r="R47" t="n">
-        <v>6795467</v>
+        <v>6795487</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5691,12 +5690,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5723,13 +5722,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446465</t>
+          <t>https://artportalen.se/Sighting/133997151</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134452196</v>
+        <v>134446465</v>
       </c>
       <c r="B48" t="n">
         <v>99112</v>
@@ -5759,7 +5758,11 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -5768,10 +5771,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451858</v>
+        <v>451867</v>
       </c>
       <c r="R48" t="n">
-        <v>6795529</v>
+        <v>6795467</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5830,13 +5833,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452196</t>
+          <t>https://artportalen.se/Sighting/134446465</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134452278</v>
+        <v>134452196</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -5875,7 +5878,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451878</v>
+        <v>451858</v>
       </c>
       <c r="R49" t="n">
         <v>6795529</v>
@@ -5937,13 +5940,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452278</t>
+          <t>https://artportalen.se/Sighting/134452196</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134452340</v>
+        <v>134452278</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -5982,10 +5985,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451934</v>
+        <v>451878</v>
       </c>
       <c r="R50" t="n">
-        <v>6795489</v>
+        <v>6795529</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6044,13 +6047,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452340</t>
+          <t>https://artportalen.se/Sighting/134452278</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134452392</v>
+        <v>134452340</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -6089,10 +6092,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451845</v>
+        <v>451934</v>
       </c>
       <c r="R51" t="n">
-        <v>6795346</v>
+        <v>6795489</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6151,13 +6154,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452392</t>
+          <t>https://artportalen.se/Sighting/134452340</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134452446</v>
+        <v>134452392</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -6196,10 +6199,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451876</v>
+        <v>451845</v>
       </c>
       <c r="R52" t="n">
-        <v>6795437</v>
+        <v>6795346</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6258,13 +6261,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452446</t>
+          <t>https://artportalen.se/Sighting/134452392</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134452468</v>
+        <v>134452446</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6303,10 +6306,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451872</v>
+        <v>451876</v>
       </c>
       <c r="R53" t="n">
-        <v>6795459</v>
+        <v>6795437</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6365,13 +6368,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452468</t>
+          <t>https://artportalen.se/Sighting/134452446</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134470975</v>
+        <v>134452468</v>
       </c>
       <c r="B54" t="n">
         <v>99112</v>
@@ -6399,33 +6402,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451828</v>
+        <v>451872</v>
       </c>
       <c r="R54" t="n">
-        <v>6795362</v>
+        <v>6795459</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6452,12 +6443,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6484,13 +6475,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134470975</t>
+          <t>https://artportalen.se/Sighting/134452468</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134471030</v>
+        <v>134470975</v>
       </c>
       <c r="B55" t="n">
         <v>99112</v>
@@ -6518,21 +6509,33 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451822</v>
+        <v>451828</v>
       </c>
       <c r="R55" t="n">
-        <v>6795403</v>
+        <v>6795362</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6591,13 +6594,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471030</t>
+          <t>https://artportalen.se/Sighting/134470975</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134471064</v>
+        <v>134471030</v>
       </c>
       <c r="B56" t="n">
         <v>99112</v>
@@ -6636,10 +6639,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451754</v>
+        <v>451822</v>
       </c>
       <c r="R56" t="n">
-        <v>6795474</v>
+        <v>6795403</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6698,13 +6701,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471064</t>
+          <t>https://artportalen.se/Sighting/134471030</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134471377</v>
+        <v>134471064</v>
       </c>
       <c r="B57" t="n">
         <v>99112</v>
@@ -6743,10 +6746,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451524</v>
+        <v>451754</v>
       </c>
       <c r="R57" t="n">
-        <v>6795576</v>
+        <v>6795474</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6805,13 +6808,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471377</t>
+          <t>https://artportalen.se/Sighting/134471064</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134519430</v>
+        <v>134471377</v>
       </c>
       <c r="B58" t="n">
         <v>99112</v>
@@ -6840,19 +6843,23 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451846</v>
+        <v>451524</v>
       </c>
       <c r="R58" t="n">
-        <v>6795506</v>
+        <v>6795576</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6876,22 +6883,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6900,33 +6897,34 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519430</t>
+          <t>https://artportalen.se/Sighting/134471377</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135087727</v>
+        <v>134519430</v>
       </c>
       <c r="B59" t="n">
-        <v>99186</v>
+        <v>99112</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6952,23 +6950,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451853</v>
+        <v>451846</v>
       </c>
       <c r="R59" t="n">
-        <v>6795315</v>
+        <v>6795506</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6992,12 +6986,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7006,34 +7010,33 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135087727</t>
+          <t>https://artportalen.se/Sighting/134519430</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135940067</v>
+        <v>135087727</v>
       </c>
       <c r="B60" t="n">
-        <v>99211</v>
+        <v>99186</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7058,29 +7061,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451650</v>
+        <v>451853</v>
       </c>
       <c r="R60" t="n">
-        <v>6795625</v>
+        <v>6795315</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7107,12 +7102,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7139,16 +7134,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135940067</t>
+          <t>https://artportalen.se/Sighting/135087727</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135370390</v>
+        <v>135940067</v>
       </c>
       <c r="B61" t="n">
-        <v>99175</v>
+        <v>99212</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7156,42 +7151,46 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451924</v>
+        <v>451650</v>
       </c>
       <c r="R61" t="n">
-        <v>6795456</v>
+        <v>6795625</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7218,17 +7217,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>I källmiljö</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7255,16 +7249,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370390</t>
+          <t>https://artportalen.se/Sighting/135940067</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135896094</v>
+        <v>135370390</v>
       </c>
       <c r="B62" t="n">
-        <v>99193</v>
+        <v>99175</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,19 +7285,23 @@
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>451940</v>
+        <v>451924</v>
       </c>
       <c r="R62" t="n">
-        <v>6795495</v>
+        <v>6795456</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7330,12 +7328,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>I källmiljö</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7362,16 +7365,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135896094</t>
+          <t>https://artportalen.se/Sighting/135370390</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135384823</v>
+        <v>135896094</v>
       </c>
       <c r="B63" t="n">
-        <v>108294</v>
+        <v>99194</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7379,21 +7382,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220083</v>
+        <v>219795</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7403,14 +7406,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>451640</v>
+        <v>451940</v>
       </c>
       <c r="R63" t="n">
-        <v>6795589</v>
+        <v>6795495</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7437,17 +7440,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Invid källbäck</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7474,16 +7472,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384823</t>
+          <t>https://artportalen.se/Sighting/135896094</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134446457</v>
+        <v>135384823</v>
       </c>
       <c r="B64" t="n">
-        <v>99099</v>
+        <v>108294</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7491,30 +7489,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220093</v>
+        <v>220083</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -7523,10 +7517,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>451867</v>
+        <v>451640</v>
       </c>
       <c r="R64" t="n">
-        <v>6795467</v>
+        <v>6795589</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7553,12 +7547,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Invid källbäck</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7585,13 +7584,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446457</t>
+          <t>https://artportalen.se/Sighting/135384823</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134452308</v>
+        <v>134446457</v>
       </c>
       <c r="B65" t="n">
         <v>99099</v>
@@ -7634,10 +7633,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451924</v>
+        <v>451867</v>
       </c>
       <c r="R65" t="n">
-        <v>6795490</v>
+        <v>6795467</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7696,13 +7695,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452308</t>
+          <t>https://artportalen.se/Sighting/134446457</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134471116</v>
+        <v>134452308</v>
       </c>
       <c r="B66" t="n">
         <v>99099</v>
@@ -7732,7 +7731,11 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -7741,10 +7744,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>451657</v>
+        <v>451924</v>
       </c>
       <c r="R66" t="n">
-        <v>6795504</v>
+        <v>6795490</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7771,12 +7774,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7803,13 +7806,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471116</t>
+          <t>https://artportalen.se/Sighting/134452308</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134471163</v>
+        <v>134471116</v>
       </c>
       <c r="B67" t="n">
         <v>99099</v>
@@ -7848,10 +7851,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451656</v>
+        <v>451657</v>
       </c>
       <c r="R67" t="n">
-        <v>6795514</v>
+        <v>6795504</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7910,13 +7913,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471163</t>
+          <t>https://artportalen.se/Sighting/134471116</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134471374</v>
+        <v>134471163</v>
       </c>
       <c r="B68" t="n">
         <v>99099</v>
@@ -7955,10 +7958,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>451524</v>
+        <v>451656</v>
       </c>
       <c r="R68" t="n">
-        <v>6795576</v>
+        <v>6795514</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8017,16 +8020,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471374</t>
+          <t>https://artportalen.se/Sighting/134471163</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134471215</v>
+        <v>134471374</v>
       </c>
       <c r="B69" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8034,21 +8037,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8058,14 +8061,14 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>451641</v>
+        <v>451524</v>
       </c>
       <c r="R69" t="n">
-        <v>6795575</v>
+        <v>6795576</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8124,13 +8127,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471215</t>
+          <t>https://artportalen.se/Sighting/134471374</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134471223</v>
+        <v>134471215</v>
       </c>
       <c r="B70" t="n">
         <v>108274</v>
@@ -8165,14 +8168,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>451640</v>
+        <v>451641</v>
       </c>
       <c r="R70" t="n">
-        <v>6795589</v>
+        <v>6795575</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8231,13 +8234,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471223</t>
+          <t>https://artportalen.se/Sighting/134471215</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134471252</v>
+        <v>134471223</v>
       </c>
       <c r="B71" t="n">
         <v>108274</v>
@@ -8276,10 +8279,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>451628</v>
+        <v>451640</v>
       </c>
       <c r="R71" t="n">
-        <v>6795600</v>
+        <v>6795589</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8338,60 +8341,55 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471252</t>
+          <t>https://artportalen.se/Sighting/134471223</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119623430</v>
+        <v>134471252</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>108274</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452010</v>
+        <v>451628</v>
       </c>
       <c r="R72" t="n">
-        <v>6795395</v>
+        <v>6795600</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8418,12 +8416,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8432,30 +8430,31 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623430</t>
+          <t>https://artportalen.se/Sighting/134471252</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120455163</v>
+        <v>119623430</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8485,7 +8484,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8493,19 +8492,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452004</v>
+        <v>452010</v>
       </c>
       <c r="R73" t="n">
-        <v>6795386</v>
+        <v>6795395</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8532,12 +8528,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8546,31 +8542,30 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120455163</t>
+          <t>https://artportalen.se/Sighting/119623430</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120493954</v>
+        <v>120455163</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8600,7 +8595,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8613,14 +8608,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>451990</v>
+        <v>452004</v>
       </c>
       <c r="R74" t="n">
-        <v>6795420</v>
+        <v>6795386</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8647,12 +8642,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8679,16 +8674,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493954</t>
+          <t>https://artportalen.se/Sighting/120455163</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133997095</v>
+        <v>120493954</v>
       </c>
       <c r="B75" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8715,12 +8710,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -8728,14 +8723,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>451903</v>
+        <v>451990</v>
       </c>
       <c r="R75" t="n">
-        <v>6795472</v>
+        <v>6795420</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8762,12 +8757,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8794,13 +8789,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997095</t>
+          <t>https://artportalen.se/Sighting/120493954</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133997219</v>
+        <v>133997095</v>
       </c>
       <c r="B76" t="n">
         <v>99195</v>
@@ -8830,7 +8825,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8847,10 +8842,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>451888</v>
+        <v>451903</v>
       </c>
       <c r="R76" t="n">
-        <v>6795475</v>
+        <v>6795472</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8909,51 +8904,63 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997219</t>
+          <t>https://artportalen.se/Sighting/133997095</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119622912</v>
+        <v>133997219</v>
       </c>
       <c r="B77" t="n">
-        <v>106229</v>
+        <v>99195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452035</v>
+        <v>451888</v>
       </c>
       <c r="R77" t="n">
-        <v>6795377</v>
+        <v>6795475</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8980,12 +8987,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8994,30 +9001,31 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119622912</t>
+          <t>https://artportalen.se/Sighting/133997219</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119623971</v>
+        <v>119622912</v>
       </c>
       <c r="B78" t="n">
         <v>106229</v>
@@ -9052,10 +9060,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>451957</v>
+        <v>452035</v>
       </c>
       <c r="R78" t="n">
-        <v>6795424</v>
+        <v>6795377</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9113,16 +9121,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623971</t>
+          <t>https://artportalen.se/Sighting/119622912</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135896078</v>
+        <v>119623971</v>
       </c>
       <c r="B79" t="n">
-        <v>106420</v>
+        <v>106229</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9148,20 +9156,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452073</v>
+        <v>451957</v>
       </c>
       <c r="R79" t="n">
-        <v>6795385</v>
+        <v>6795424</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9188,12 +9192,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9202,34 +9206,33 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135896078</t>
+          <t>https://artportalen.se/Sighting/119623971</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134452234</v>
+        <v>135896078</v>
       </c>
       <c r="B80" t="n">
-        <v>98060</v>
+        <v>106421</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9237,21 +9240,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9261,14 +9264,14 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>451878</v>
+        <v>452073</v>
       </c>
       <c r="R80" t="n">
-        <v>6795529</v>
+        <v>6795385</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9295,12 +9298,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9327,13 +9330,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452234</t>
+          <t>https://artportalen.se/Sighting/135896078</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134452406</v>
+        <v>134452234</v>
       </c>
       <c r="B81" t="n">
         <v>98060</v>
@@ -9372,10 +9375,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>451858</v>
+        <v>451878</v>
       </c>
       <c r="R81" t="n">
-        <v>6795410</v>
+        <v>6795529</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9434,13 +9437,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452406</t>
+          <t>https://artportalen.se/Sighting/134452234</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134452426</v>
+        <v>134452406</v>
       </c>
       <c r="B82" t="n">
         <v>98060</v>
@@ -9479,10 +9482,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>451875</v>
+        <v>451858</v>
       </c>
       <c r="R82" t="n">
-        <v>6795422</v>
+        <v>6795410</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9541,13 +9544,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452426</t>
+          <t>https://artportalen.se/Sighting/134452406</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134519426</v>
+        <v>134452426</v>
       </c>
       <c r="B83" t="n">
         <v>98060</v>
@@ -9576,19 +9579,23 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>451669</v>
+        <v>451875</v>
       </c>
       <c r="R83" t="n">
-        <v>6795570</v>
+        <v>6795422</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9612,22 +9619,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9636,33 +9633,34 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519426</t>
+          <t>https://artportalen.se/Sighting/134452426</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135370746</v>
+        <v>134519426</v>
       </c>
       <c r="B84" t="n">
-        <v>98138</v>
+        <v>98060</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9688,23 +9686,19 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>451924</v>
+        <v>451669</v>
       </c>
       <c r="R84" t="n">
-        <v>6795456</v>
+        <v>6795570</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9728,12 +9722,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9742,31 +9746,30 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370746</t>
+          <t>https://artportalen.se/Sighting/134519426</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135370757</v>
+        <v>135370746</v>
       </c>
       <c r="B85" t="n">
         <v>98138</v>
@@ -9801,17 +9804,17 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>451910</v>
+        <v>451924</v>
       </c>
       <c r="R85" t="n">
-        <v>6795497</v>
+        <v>6795456</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9867,16 +9870,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370757</t>
+          <t>https://artportalen.se/Sighting/135370746</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134470979</v>
+        <v>135370757</v>
       </c>
       <c r="B86" t="n">
-        <v>99217</v>
+        <v>98138</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9884,21 +9887,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9908,17 +9911,17 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451828</v>
+        <v>451910</v>
       </c>
       <c r="R86" t="n">
-        <v>6795362</v>
+        <v>6795497</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9942,12 +9945,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9974,13 +9977,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134470979</t>
+          <t>https://artportalen.se/Sighting/135370757</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134471102</v>
+        <v>134470979</v>
       </c>
       <c r="B87" t="n">
         <v>99217</v>
@@ -10015,14 +10018,14 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>451693</v>
+        <v>451828</v>
       </c>
       <c r="R87" t="n">
-        <v>6795486</v>
+        <v>6795362</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10081,13 +10084,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471102</t>
+          <t>https://artportalen.se/Sighting/134470979</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134471378</v>
+        <v>134471102</v>
       </c>
       <c r="B88" t="n">
         <v>99217</v>
@@ -10126,10 +10129,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>451524</v>
+        <v>451693</v>
       </c>
       <c r="R88" t="n">
-        <v>6795576</v>
+        <v>6795486</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10188,16 +10191,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471378</t>
+          <t>https://artportalen.se/Sighting/134471102</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132724578</v>
+        <v>134471378</v>
       </c>
       <c r="B89" t="n">
-        <v>101403</v>
+        <v>99217</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10205,57 +10208,41 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>451910</v>
+        <v>451524</v>
       </c>
       <c r="R89" t="n">
-        <v>6795497</v>
+        <v>6795576</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10279,12 +10266,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10310,6 +10297,129 @@
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471378</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>132724578</v>
+      </c>
+      <c r="B90" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>451910</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6795497</v>
+      </c>
+      <c r="S90" t="n">
+        <v>25</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132724578</t>
         </is>
@@ -10405,6 +10515,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4140,7 +4140,7 @@
         <v>136240267</v>
       </c>
       <c r="B34" t="n">
-        <v>57823</v>
+        <v>57824</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>135940024</v>
       </c>
       <c r="B40" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135940067</v>
       </c>
       <c r="B61" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>135896094</v>
       </c>
       <c r="B63" t="n">
-        <v>99194</v>
+        <v>99195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135896078</v>
       </c>
       <c r="B80" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4140,7 +4140,7 @@
         <v>136240267</v>
       </c>
       <c r="B34" t="n">
-        <v>57824</v>
+        <v>57828</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>135940024</v>
       </c>
       <c r="B40" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135940067</v>
       </c>
       <c r="B61" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>135896094</v>
       </c>
       <c r="B63" t="n">
-        <v>99195</v>
+        <v>99201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135896078</v>
       </c>
       <c r="B80" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4140,7 +4140,7 @@
         <v>136240267</v>
       </c>
       <c r="B34" t="n">
-        <v>57828</v>
+        <v>57829</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>135940024</v>
       </c>
       <c r="B40" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135940067</v>
       </c>
       <c r="B61" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>135896094</v>
       </c>
       <c r="B63" t="n">
-        <v>99201</v>
+        <v>99202</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135896078</v>
       </c>
       <c r="B80" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -7143,7 +7143,7 @@
         <v>135940067</v>
       </c>
       <c r="B61" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>135896094</v>
       </c>
       <c r="B63" t="n">
-        <v>99202</v>
+        <v>99213</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135896078</v>
       </c>
       <c r="B80" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4140,7 +4140,7 @@
         <v>136240267</v>
       </c>
       <c r="B34" t="n">
-        <v>57829</v>
+        <v>57834</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>135940024</v>
       </c>
       <c r="B40" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135940067</v>
       </c>
       <c r="B61" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>135896094</v>
       </c>
       <c r="B63" t="n">
-        <v>99213</v>
+        <v>99226</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135896078</v>
       </c>
       <c r="B80" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -7143,7 +7143,7 @@
         <v>135940067</v>
       </c>
       <c r="B61" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>135896094</v>
       </c>
       <c r="B63" t="n">
-        <v>99226</v>
+        <v>99227</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135896078</v>
       </c>
       <c r="B80" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4140,7 +4140,7 @@
         <v>136240267</v>
       </c>
       <c r="B34" t="n">
-        <v>57834</v>
+        <v>57847</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>135940024</v>
       </c>
       <c r="B40" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>135940067</v>
       </c>
       <c r="B61" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>135896094</v>
       </c>
       <c r="B63" t="n">
-        <v>99227</v>
+        <v>99240</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135896078</v>
       </c>
       <c r="B80" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -7143,7 +7143,7 @@
         <v>135940067</v>
       </c>
       <c r="B61" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>135896094</v>
       </c>
       <c r="B63" t="n">
-        <v>99240</v>
+        <v>99241</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>135896078</v>
       </c>
       <c r="B80" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
